--- a/jogos_2026-05-01.xlsx
+++ b/jogos_2026-05-01.xlsx
@@ -950,22 +950,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>5.84</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.41</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>5.84</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13208,17 +13208,17 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13405,7 +13405,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,22 +14346,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>4.58</v>
+        <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18576,10 +18576,10 @@
         <v>0</v>
       </c>
       <c r="AE92" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF92" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG92" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -18970,10 +18970,10 @@
         <v>0</v>
       </c>
       <c r="AE94" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF94" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG94" t="n">
         <v>0</v>
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,22 +23408,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,22 +24590,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G135" t="n">

--- a/jogos_2026-05-01.xlsx
+++ b/jogos_2026-05-01.xlsx
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>5.84</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Jamshedpur</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Jamshedpur</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>5.84</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>4.41</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13208,7 +13208,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P65" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13602,17 +13602,17 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P67" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,22 +14346,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q93" t="n">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18773,10 +18773,10 @@
         <v>0</v>
       </c>
       <c r="AE93" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF93" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG93" t="n">
         <v>0</v>
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>4.58</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -18970,10 +18970,10 @@
         <v>0</v>
       </c>
       <c r="AE94" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF94" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG94" t="n">
         <v>0</v>
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,22 +23999,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24984,22 +24984,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G135" t="n">

--- a/jogos_2026-05-01.xlsx
+++ b/jogos_2026-05-01.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kuching FA</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Kuching FA</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>5.84</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.41</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Jamshedpur</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>5.84</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Jamshedpur</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13602,17 +13602,17 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13799,17 +13799,17 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P68" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>4.58</v>
+        <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18773,10 +18773,10 @@
         <v>0</v>
       </c>
       <c r="AE93" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF93" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG93" t="n">
         <v>0</v>
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q95" t="n">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19167,10 +19167,10 @@
         <v>0</v>
       </c>
       <c r="AE95" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF95" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG95" t="n">
         <v>0</v>
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,22 +23408,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,22 +23999,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24984,22 +24984,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G135" t="n">

--- a/jogos_2026-05-01.xlsx
+++ b/jogos_2026-05-01.xlsx
@@ -950,22 +950,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Jamshedpur</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>5.84</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Jamshedpur</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>5.84</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.41</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13799,17 +13799,17 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -13996,7 +13996,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P69" t="n">
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,22 +14346,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q92" t="n">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18576,10 +18576,10 @@
         <v>0</v>
       </c>
       <c r="AE92" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF92" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG92" t="n">
         <v>0</v>
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Q95" t="n">
-        <v>4.58</v>
+        <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19167,10 +19167,10 @@
         <v>0</v>
       </c>
       <c r="AE95" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF95" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG95" t="n">
         <v>0</v>
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,22 +22029,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,22 +23408,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25772,22 +25772,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G135" t="n">

--- a/jogos_2026-05-01.xlsx
+++ b/jogos_2026-05-01.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1147,22 +1147,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Jamshedpur</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>5.84</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>5.84</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.41</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Jamshedpur</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13405,7 +13405,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P66" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13651,10 +13651,10 @@
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF67" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -13996,17 +13996,17 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>4.58</v>
+        <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18576,10 +18576,10 @@
         <v>0</v>
       </c>
       <c r="AE92" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF92" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG92" t="n">
         <v>0</v>
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -18970,10 +18970,10 @@
         <v>0</v>
       </c>
       <c r="AE94" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF94" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG94" t="n">
         <v>0</v>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,22 +22029,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,22 +25378,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,22 +25772,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G135" t="n">

--- a/jogos_2026-05-01.xlsx
+++ b/jogos_2026-05-01.xlsx
@@ -950,22 +950,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1147,22 +1147,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Kuching FA</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kuching FA</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Jamshedpur</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Jamshedpur</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>2.34</v>
+        <v>3.76</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="R67" t="n">
-        <v>2.93</v>
+        <v>1.98</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13651,10 +13651,10 @@
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF67" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG67" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>3.76</v>
+        <v>2.34</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="R69" t="n">
-        <v>1.98</v>
+        <v>2.93</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,10 +14045,10 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF69" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>4.58</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -18970,10 +18970,10 @@
         <v>0</v>
       </c>
       <c r="AE94" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF94" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG94" t="n">
         <v>0</v>
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q95" t="n">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19167,10 +19167,10 @@
         <v>0</v>
       </c>
       <c r="AE95" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF95" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG95" t="n">
         <v>0</v>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,22 +23605,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25378,22 +25378,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,22 +25969,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G135" t="n">

--- a/jogos_2026-05-01.xlsx
+++ b/jogos_2026-05-01.xlsx
@@ -950,22 +950,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1147,22 +1147,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kuching FA</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Kuching FA</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>5.84</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Jamshedpur</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>5.84</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>4.41</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Jamshedpur</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13405,17 +13405,17 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13454,10 +13454,10 @@
         <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF66" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13602,17 +13602,17 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P67" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>2.34</v>
+        <v>2.58</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.25</v>
+        <v>3.12</v>
       </c>
       <c r="R69" t="n">
-        <v>2.93</v>
+        <v>2.73</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,10 +14045,10 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF69" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Q89" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R89" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q92" t="n">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18576,10 +18576,10 @@
         <v>0</v>
       </c>
       <c r="AE92" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF92" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG92" t="n">
         <v>0</v>
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Q95" t="n">
-        <v>4.58</v>
+        <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19167,10 +19167,10 @@
         <v>0</v>
       </c>
       <c r="AE95" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF95" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG95" t="n">
         <v>0</v>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,22 +23605,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,22 +25772,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,22 +25969,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26954,22 +26954,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G135" t="n">

--- a/jogos_2026-05-01.xlsx
+++ b/jogos_2026-05-01.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI136"/>
+  <dimension ref="A1:BI128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Kuching FA</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kuching FA</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Jamshedpur</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Jamshedpur</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>2.34</v>
+        <v>2.58</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.25</v>
+        <v>3.12</v>
       </c>
       <c r="R66" t="n">
-        <v>2.93</v>
+        <v>2.73</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13454,10 +13454,10 @@
         <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF66" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG66" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>3.76</v>
+        <v>2.34</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="R68" t="n">
-        <v>1.98</v>
+        <v>2.93</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13848,10 +13848,10 @@
         <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF68" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R79" t="n">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16015,10 +16015,10 @@
         <v>0</v>
       </c>
       <c r="AE79" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF79" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG79" t="n">
         <v>0</v>
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>4.51</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q87" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R87" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17591,10 +17591,10 @@
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF87" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG87" t="n">
         <v>0</v>
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q90" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>6.12</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18182,10 +18182,10 @@
         <v>0</v>
       </c>
       <c r="AE90" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF90" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG90" t="n">
         <v>0</v>
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q96" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,22 +24590,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25570,27 +25570,27 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25758,1582 +25758,6 @@
         <v>0</v>
       </c>
       <c r="BI128" s="3" t="n">
-        <v>46143.875</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="2" t="n">
-        <v>46143</v>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Ecuador Primera Categoría Serie A</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>Libertad</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>SD Aucas</t>
-        </is>
-      </c>
-      <c r="G129" t="n">
-        <v>0</v>
-      </c>
-      <c r="H129" t="n">
-        <v>0</v>
-      </c>
-      <c r="I129" t="n">
-        <v>0</v>
-      </c>
-      <c r="J129" t="n">
-        <v>0</v>
-      </c>
-      <c r="K129" t="n">
-        <v>0</v>
-      </c>
-      <c r="L129" t="n">
-        <v>0</v>
-      </c>
-      <c r="M129" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N129" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O129" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P129" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
-      <c r="R129" t="n">
-        <v>0</v>
-      </c>
-      <c r="S129" t="n">
-        <v>0</v>
-      </c>
-      <c r="T129" t="n">
-        <v>0</v>
-      </c>
-      <c r="U129" t="n">
-        <v>0</v>
-      </c>
-      <c r="V129" t="n">
-        <v>0</v>
-      </c>
-      <c r="W129" t="n">
-        <v>0</v>
-      </c>
-      <c r="X129" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y129" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ129" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA129" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB129" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC129" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD129" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE129" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF129" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG129" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH129" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI129" s="3" t="n">
-        <v>46143.875</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="2" t="n">
-        <v>46143</v>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Turkey 1. Lig</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>İstanbulspor</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>Adana Demirspor</t>
-        </is>
-      </c>
-      <c r="G130" t="n">
-        <v>0</v>
-      </c>
-      <c r="H130" t="n">
-        <v>0</v>
-      </c>
-      <c r="I130" t="n">
-        <v>0</v>
-      </c>
-      <c r="J130" t="n">
-        <v>0</v>
-      </c>
-      <c r="K130" t="n">
-        <v>0</v>
-      </c>
-      <c r="L130" t="n">
-        <v>0</v>
-      </c>
-      <c r="M130" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N130" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O130" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P130" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
-      <c r="R130" t="n">
-        <v>0</v>
-      </c>
-      <c r="S130" t="n">
-        <v>0</v>
-      </c>
-      <c r="T130" t="n">
-        <v>0</v>
-      </c>
-      <c r="U130" t="n">
-        <v>0</v>
-      </c>
-      <c r="V130" t="n">
-        <v>0</v>
-      </c>
-      <c r="W130" t="n">
-        <v>0</v>
-      </c>
-      <c r="X130" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y130" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ130" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA130" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB130" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC130" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD130" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE130" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF130" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG130" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH130" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI130" s="3" t="n">
-        <v>46143.875</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="2" t="n">
-        <v>46143</v>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>OFK Vršac</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>Jedinstvo Ub</t>
-        </is>
-      </c>
-      <c r="G131" t="n">
-        <v>0</v>
-      </c>
-      <c r="H131" t="n">
-        <v>0</v>
-      </c>
-      <c r="I131" t="n">
-        <v>0</v>
-      </c>
-      <c r="J131" t="n">
-        <v>0</v>
-      </c>
-      <c r="K131" t="n">
-        <v>0</v>
-      </c>
-      <c r="L131" t="n">
-        <v>0</v>
-      </c>
-      <c r="M131" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N131" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O131" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P131" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
-      <c r="R131" t="n">
-        <v>0</v>
-      </c>
-      <c r="S131" t="n">
-        <v>0</v>
-      </c>
-      <c r="T131" t="n">
-        <v>0</v>
-      </c>
-      <c r="U131" t="n">
-        <v>0</v>
-      </c>
-      <c r="V131" t="n">
-        <v>0</v>
-      </c>
-      <c r="W131" t="n">
-        <v>0</v>
-      </c>
-      <c r="X131" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y131" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ131" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA131" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB131" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC131" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD131" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE131" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF131" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG131" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH131" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI131" s="3" t="n">
-        <v>46143.875</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="2" t="n">
-        <v>46143</v>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Tunisia Ligue 1</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>Ben Guerdane</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>AS Slimane</t>
-        </is>
-      </c>
-      <c r="G132" t="n">
-        <v>0</v>
-      </c>
-      <c r="H132" t="n">
-        <v>0</v>
-      </c>
-      <c r="I132" t="n">
-        <v>0</v>
-      </c>
-      <c r="J132" t="n">
-        <v>0</v>
-      </c>
-      <c r="K132" t="n">
-        <v>0</v>
-      </c>
-      <c r="L132" t="n">
-        <v>0</v>
-      </c>
-      <c r="M132" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N132" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O132" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P132" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
-      <c r="R132" t="n">
-        <v>0</v>
-      </c>
-      <c r="S132" t="n">
-        <v>0</v>
-      </c>
-      <c r="T132" t="n">
-        <v>0</v>
-      </c>
-      <c r="U132" t="n">
-        <v>0</v>
-      </c>
-      <c r="V132" t="n">
-        <v>0</v>
-      </c>
-      <c r="W132" t="n">
-        <v>0</v>
-      </c>
-      <c r="X132" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y132" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ132" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA132" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB132" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC132" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD132" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE132" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF132" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG132" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH132" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI132" s="3" t="n">
-        <v>46143.875</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="2" t="n">
-        <v>46143</v>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Turkey 1. Lig</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>Bandırmaspor</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>Sivasspor</t>
-        </is>
-      </c>
-      <c r="G133" t="n">
-        <v>0</v>
-      </c>
-      <c r="H133" t="n">
-        <v>0</v>
-      </c>
-      <c r="I133" t="n">
-        <v>0</v>
-      </c>
-      <c r="J133" t="n">
-        <v>0</v>
-      </c>
-      <c r="K133" t="n">
-        <v>0</v>
-      </c>
-      <c r="L133" t="n">
-        <v>0</v>
-      </c>
-      <c r="M133" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N133" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O133" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P133" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
-      <c r="R133" t="n">
-        <v>0</v>
-      </c>
-      <c r="S133" t="n">
-        <v>0</v>
-      </c>
-      <c r="T133" t="n">
-        <v>0</v>
-      </c>
-      <c r="U133" t="n">
-        <v>0</v>
-      </c>
-      <c r="V133" t="n">
-        <v>0</v>
-      </c>
-      <c r="W133" t="n">
-        <v>0</v>
-      </c>
-      <c r="X133" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y133" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ133" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA133" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB133" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC133" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD133" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE133" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF133" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG133" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH133" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI133" s="3" t="n">
-        <v>46143.875</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="2" t="n">
-        <v>46143</v>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>Sarajevo</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>Borac Banja Luka</t>
-        </is>
-      </c>
-      <c r="G134" t="n">
-        <v>0</v>
-      </c>
-      <c r="H134" t="n">
-        <v>0</v>
-      </c>
-      <c r="I134" t="n">
-        <v>0</v>
-      </c>
-      <c r="J134" t="n">
-        <v>0</v>
-      </c>
-      <c r="K134" t="n">
-        <v>0</v>
-      </c>
-      <c r="L134" t="n">
-        <v>0</v>
-      </c>
-      <c r="M134" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N134" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O134" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P134" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
-      <c r="R134" t="n">
-        <v>0</v>
-      </c>
-      <c r="S134" t="n">
-        <v>0</v>
-      </c>
-      <c r="T134" t="n">
-        <v>0</v>
-      </c>
-      <c r="U134" t="n">
-        <v>0</v>
-      </c>
-      <c r="V134" t="n">
-        <v>0</v>
-      </c>
-      <c r="W134" t="n">
-        <v>0</v>
-      </c>
-      <c r="X134" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y134" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ134" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA134" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB134" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC134" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD134" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE134" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF134" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG134" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH134" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI134" s="3" t="n">
-        <v>46143.875</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="2" t="n">
-        <v>46143</v>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>Houston Dash</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>Seattle Reign</t>
-        </is>
-      </c>
-      <c r="G135" t="n">
-        <v>0</v>
-      </c>
-      <c r="H135" t="n">
-        <v>0</v>
-      </c>
-      <c r="I135" t="n">
-        <v>0</v>
-      </c>
-      <c r="J135" t="n">
-        <v>0</v>
-      </c>
-      <c r="K135" t="n">
-        <v>0</v>
-      </c>
-      <c r="L135" t="n">
-        <v>0</v>
-      </c>
-      <c r="M135" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N135" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O135" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P135" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
-      <c r="R135" t="n">
-        <v>0</v>
-      </c>
-      <c r="S135" t="n">
-        <v>0</v>
-      </c>
-      <c r="T135" t="n">
-        <v>0</v>
-      </c>
-      <c r="U135" t="n">
-        <v>0</v>
-      </c>
-      <c r="V135" t="n">
-        <v>0</v>
-      </c>
-      <c r="W135" t="n">
-        <v>0</v>
-      </c>
-      <c r="X135" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y135" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ135" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA135" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB135" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC135" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD135" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE135" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF135" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG135" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH135" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI135" s="3" t="n">
-        <v>46143.875</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="2" t="n">
-        <v>46143</v>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>USA MLS Next Pro</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>LA Galaxy II</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>San Jose Earthquakes II</t>
-        </is>
-      </c>
-      <c r="G136" t="n">
-        <v>0</v>
-      </c>
-      <c r="H136" t="n">
-        <v>0</v>
-      </c>
-      <c r="I136" t="n">
-        <v>0</v>
-      </c>
-      <c r="J136" t="n">
-        <v>0</v>
-      </c>
-      <c r="K136" t="n">
-        <v>0</v>
-      </c>
-      <c r="L136" t="n">
-        <v>0</v>
-      </c>
-      <c r="M136" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N136" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O136" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P136" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
-      <c r="R136" t="n">
-        <v>0</v>
-      </c>
-      <c r="S136" t="n">
-        <v>0</v>
-      </c>
-      <c r="T136" t="n">
-        <v>0</v>
-      </c>
-      <c r="U136" t="n">
-        <v>0</v>
-      </c>
-      <c r="V136" t="n">
-        <v>0</v>
-      </c>
-      <c r="W136" t="n">
-        <v>0</v>
-      </c>
-      <c r="X136" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y136" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ136" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA136" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB136" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC136" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD136" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE136" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF136" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG136" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH136" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI136" s="3" t="n">
         <v>46143.95833333334</v>
       </c>
     </row>

--- a/jogos_2026-05-01.xlsx
+++ b/jogos_2026-05-01.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kuching FA</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Kuching FA</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>5.84</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.41</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>5.84</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10795,27 +10795,27 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10983,7 +10983,7 @@
         <v>0</v>
       </c>
       <c r="BI53" s="3" t="n">
-        <v>46143.52083333334</v>
+        <v>46143.5</v>
       </c>
     </row>
     <row r="54">
@@ -10992,12 +10992,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11180,7 +11180,7 @@
         <v>0</v>
       </c>
       <c r="BI54" s="3" t="n">
-        <v>46143.54166666666</v>
+        <v>46143.52083333334</v>
       </c>
     </row>
     <row r="55">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13208,17 +13208,17 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>2.58</v>
+        <v>2.34</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
       <c r="R66" t="n">
-        <v>2.73</v>
+        <v>2.93</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13454,10 +13454,10 @@
         <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF66" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13602,17 +13602,17 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13848,10 +13848,10 @@
         <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF68" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15818,10 +15818,10 @@
         <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF78" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG78" t="n">
         <v>0</v>
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1.74</v>
+        <v>2.1</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.62</v>
+        <v>3.15</v>
       </c>
       <c r="R79" t="n">
-        <v>4.02</v>
+        <v>3.35</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16015,10 +16015,10 @@
         <v>0</v>
       </c>
       <c r="AE79" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF79" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>4.51</v>
+        <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Q82" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R82" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q83" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q84" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R84" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q85" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R85" t="n">
-        <v>0</v>
+        <v>6.12</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17197,10 +17197,10 @@
         <v>0</v>
       </c>
       <c r="AE85" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF85" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG85" t="n">
         <v>0</v>
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="Q87" t="n">
         <v>3.62</v>
       </c>
       <c r="R87" t="n">
-        <v>4.4</v>
+        <v>4.02</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17591,10 +17591,10 @@
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AF87" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AG87" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>4.51</v>
       </c>
       <c r="Q88" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R88" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>6.12</v>
+        <v>0</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18182,10 +18182,10 @@
         <v>0</v>
       </c>
       <c r="AE90" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF90" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG90" t="n">
         <v>0</v>
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>1.5</v>
+        <v>1.92</v>
       </c>
       <c r="Q92" t="n">
-        <v>4.58</v>
+        <v>3.3</v>
       </c>
       <c r="R92" t="n">
-        <v>7.8</v>
+        <v>4.14</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18576,10 +18576,10 @@
         <v>0</v>
       </c>
       <c r="AE92" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF92" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG92" t="n">
         <v>0</v>
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>6.15</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>8.949999999999999</v>
+        <v>0</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Q95" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1.92</v>
+        <v>1.5</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.3</v>
+        <v>4.58</v>
       </c>
       <c r="R96" t="n">
-        <v>4.14</v>
+        <v>7.8</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,10 +19364,10 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF96" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,22 +23211,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,22 +24590,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G127" t="n">

--- a/jogos_2026-05-01.xlsx
+++ b/jogos_2026-05-01.xlsx
@@ -1147,22 +1147,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Jamshedpur</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>5.84</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.41</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>5.84</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Jamshedpur</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13208,17 +13208,17 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13405,17 +13405,17 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P66" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13454,10 +13454,10 @@
         <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF66" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>2.58</v>
+        <v>2.34</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
       <c r="R69" t="n">
-        <v>2.73</v>
+        <v>2.93</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,10 +14045,10 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF69" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>1.92</v>
+        <v>1.45</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.91</v>
+        <v>4.05</v>
       </c>
       <c r="R75" t="n">
-        <v>3.71</v>
+        <v>6.12</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15227,10 +15227,10 @@
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF75" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG75" t="n">
         <v>0</v>
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2.87</v>
+        <v>2.37</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="R77" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>1.68</v>
+        <v>2.32</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.62</v>
+        <v>3.1</v>
       </c>
       <c r="R78" t="n">
-        <v>4.4</v>
+        <v>2.99</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15818,10 +15818,10 @@
         <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF78" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG78" t="n">
         <v>0</v>
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>2.1</v>
+        <v>1.68</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.15</v>
+        <v>3.62</v>
       </c>
       <c r="R79" t="n">
-        <v>3.35</v>
+        <v>4.4</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16015,10 +16015,10 @@
         <v>0</v>
       </c>
       <c r="AE79" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF79" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG79" t="n">
         <v>0</v>
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>3.74</v>
+        <v>1.92</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.45</v>
+        <v>3.91</v>
       </c>
       <c r="R81" t="n">
-        <v>1.88</v>
+        <v>3.71</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>1.45</v>
+        <v>2.87</v>
       </c>
       <c r="Q85" t="n">
-        <v>4.05</v>
+        <v>3.4</v>
       </c>
       <c r="R85" t="n">
-        <v>6.12</v>
+        <v>2.3</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17197,10 +17197,10 @@
         <v>0</v>
       </c>
       <c r="AE85" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF85" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG85" t="n">
         <v>0</v>
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q86" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R86" t="n">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17394,10 +17394,10 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF86" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG86" t="n">
         <v>0</v>
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>1.74</v>
+        <v>1.42</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.62</v>
+        <v>4.3</v>
       </c>
       <c r="R87" t="n">
-        <v>4.02</v>
+        <v>6.55</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17591,10 +17591,10 @@
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF87" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG87" t="n">
         <v>0</v>
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Q91" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -18970,10 +18970,10 @@
         <v>0</v>
       </c>
       <c r="AE94" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF94" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG94" t="n">
         <v>0</v>
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>1.26</v>
+        <v>1.92</v>
       </c>
       <c r="Q95" t="n">
-        <v>6.15</v>
+        <v>3.3</v>
       </c>
       <c r="R95" t="n">
-        <v>8.949999999999999</v>
+        <v>4.14</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Q96" t="n">
-        <v>4.58</v>
+        <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,10 +19364,10 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF96" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,22 +23211,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,22 +23605,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,22 +23999,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G127" t="n">

--- a/jogos_2026-05-01.xlsx
+++ b/jogos_2026-05-01.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Jamshedpur</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>5.84</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.41</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Jamshedpur</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>5.84</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13405,17 +13405,17 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13602,7 +13602,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P67" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>2.58</v>
+        <v>2.34</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
       <c r="R68" t="n">
-        <v>2.73</v>
+        <v>2.93</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13848,10 +13848,10 @@
         <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF68" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG68" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>2.34</v>
+        <v>2.58</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.25</v>
+        <v>3.12</v>
       </c>
       <c r="R69" t="n">
-        <v>2.93</v>
+        <v>2.73</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,10 +14045,10 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF69" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>1.45</v>
+        <v>4.51</v>
       </c>
       <c r="Q75" t="n">
-        <v>4.05</v>
+        <v>3.58</v>
       </c>
       <c r="R75" t="n">
-        <v>6.12</v>
+        <v>1.77</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15227,10 +15227,10 @@
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF75" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG75" t="n">
         <v>0</v>
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>2.1</v>
+        <v>1.74</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.15</v>
+        <v>3.62</v>
       </c>
       <c r="R76" t="n">
-        <v>3.35</v>
+        <v>4.02</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15424,10 +15424,10 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF76" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG76" t="n">
         <v>0</v>
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2.37</v>
+        <v>1.68</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.2</v>
+        <v>3.62</v>
       </c>
       <c r="R77" t="n">
-        <v>2.7</v>
+        <v>4.4</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15621,10 +15621,10 @@
         <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF77" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG77" t="n">
         <v>0</v>
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>2.32</v>
+        <v>3.74</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="R78" t="n">
-        <v>2.99</v>
+        <v>1.88</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1.68</v>
+        <v>2.1</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.62</v>
+        <v>3.15</v>
       </c>
       <c r="R79" t="n">
-        <v>4.4</v>
+        <v>3.35</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16015,10 +16015,10 @@
         <v>0</v>
       </c>
       <c r="AE79" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF79" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG79" t="n">
         <v>0</v>
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1.92</v>
+        <v>1.42</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.91</v>
+        <v>4.3</v>
       </c>
       <c r="R81" t="n">
-        <v>3.71</v>
+        <v>6.55</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Q83" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q84" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R84" t="n">
-        <v>0</v>
+        <v>6.12</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17000,10 +17000,10 @@
         <v>0</v>
       </c>
       <c r="AE84" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF84" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG84" t="n">
         <v>0</v>
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>4.02</v>
+        <v>0</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17394,10 +17394,10 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF86" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG86" t="n">
         <v>0</v>
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>1.42</v>
+        <v>2.32</v>
       </c>
       <c r="Q87" t="n">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="R87" t="n">
-        <v>6.55</v>
+        <v>2.99</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>4.51</v>
+        <v>2.37</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.58</v>
+        <v>3.2</v>
       </c>
       <c r="R88" t="n">
-        <v>1.77</v>
+        <v>2.7</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q90" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1.26</v>
+        <v>1.5</v>
       </c>
       <c r="Q91" t="n">
-        <v>6.15</v>
+        <v>4.58</v>
       </c>
       <c r="R91" t="n">
-        <v>8.949999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18379,10 +18379,10 @@
         <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF91" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG91" t="n">
         <v>0</v>
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q93" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>4.58</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -18970,10 +18970,10 @@
         <v>0</v>
       </c>
       <c r="AE94" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF94" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG94" t="n">
         <v>0</v>
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>1.92</v>
+        <v>1.26</v>
       </c>
       <c r="Q95" t="n">
-        <v>3.3</v>
+        <v>6.15</v>
       </c>
       <c r="R95" t="n">
-        <v>4.14</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,22 +23605,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,22 +23999,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G127" t="n">

--- a/jogos_2026-05-01.xlsx
+++ b/jogos_2026-05-01.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Jamshedpur</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>5.84</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Jamshedpur</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>5.84</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>4.41</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>3.76</v>
+        <v>2.58</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="R66" t="n">
-        <v>1.98</v>
+        <v>2.73</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13602,17 +13602,17 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13651,10 +13651,10 @@
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF67" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG67" t="n">
         <v>0</v>
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13799,17 +13799,17 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P68" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13848,10 +13848,10 @@
         <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF68" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,22 +14346,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>4.51</v>
+        <v>2.32</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.58</v>
+        <v>3.1</v>
       </c>
       <c r="R75" t="n">
-        <v>1.77</v>
+        <v>2.99</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>1.74</v>
+        <v>2.87</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.62</v>
+        <v>3.4</v>
       </c>
       <c r="R76" t="n">
-        <v>4.02</v>
+        <v>2.3</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15424,10 +15424,10 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF76" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG76" t="n">
         <v>0</v>
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1.68</v>
+        <v>2.37</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.62</v>
+        <v>3.2</v>
       </c>
       <c r="R77" t="n">
-        <v>4.4</v>
+        <v>2.7</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15621,10 +15621,10 @@
         <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF77" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG77" t="n">
         <v>0</v>
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>3.74</v>
+        <v>2.1</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="R78" t="n">
-        <v>1.88</v>
+        <v>3.35</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>2.1</v>
+        <v>1.42</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.15</v>
+        <v>4.3</v>
       </c>
       <c r="R79" t="n">
-        <v>3.35</v>
+        <v>6.55</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q82" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R82" t="n">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16606,10 +16606,10 @@
         <v>0</v>
       </c>
       <c r="AE82" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF82" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG82" t="n">
         <v>0</v>
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>2.87</v>
+        <v>4.51</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.4</v>
+        <v>3.58</v>
       </c>
       <c r="R83" t="n">
-        <v>2.3</v>
+        <v>1.77</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>6.12</v>
+        <v>0</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17000,10 +17000,10 @@
         <v>0</v>
       </c>
       <c r="AE84" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF84" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG84" t="n">
         <v>0</v>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>2.32</v>
+        <v>3.74</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="R87" t="n">
-        <v>2.99</v>
+        <v>1.88</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>2.37</v>
+        <v>1.45</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.2</v>
+        <v>4.05</v>
       </c>
       <c r="R88" t="n">
-        <v>2.7</v>
+        <v>6.12</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17788,10 +17788,10 @@
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF88" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG88" t="n">
         <v>0</v>
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q89" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="R89" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1.92</v>
+        <v>1.68</v>
       </c>
       <c r="Q90" t="n">
-        <v>3.91</v>
+        <v>3.62</v>
       </c>
       <c r="R90" t="n">
-        <v>3.71</v>
+        <v>4.4</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18182,10 +18182,10 @@
         <v>0</v>
       </c>
       <c r="AE90" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF90" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG90" t="n">
         <v>0</v>
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1.5</v>
+        <v>1.26</v>
       </c>
       <c r="Q91" t="n">
-        <v>4.58</v>
+        <v>6.15</v>
       </c>
       <c r="R91" t="n">
-        <v>7.8</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18379,10 +18379,10 @@
         <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF91" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG91" t="n">
         <v>0</v>
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q92" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>1.92</v>
+        <v>1.5</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.3</v>
+        <v>4.58</v>
       </c>
       <c r="R93" t="n">
-        <v>4.14</v>
+        <v>7.8</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18773,10 +18773,10 @@
         <v>0</v>
       </c>
       <c r="AE93" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF93" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG93" t="n">
         <v>0</v>
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Q95" t="n">
-        <v>6.15</v>
+        <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>8.949999999999999</v>
+        <v>0</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G127" t="n">

--- a/jogos_2026-05-01.xlsx
+++ b/jogos_2026-05-01.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3801,10 +3801,10 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -3998,10 +3998,10 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4195,10 +4195,10 @@
         <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4392,10 +4392,10 @@
         <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG20" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -4983,10 +4983,10 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5574,10 +5574,10 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5771,10 +5771,10 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>5.84</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>5.84</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.41</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Jamshedpur</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Jamshedpur</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>3.76</v>
+        <v>2.58</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="R65" t="n">
-        <v>1.98</v>
+        <v>2.73</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>2.58</v>
+        <v>2.34</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
       <c r="R66" t="n">
-        <v>2.73</v>
+        <v>2.93</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13454,10 +13454,10 @@
         <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF66" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>2.34</v>
+        <v>3.76</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="R67" t="n">
-        <v>2.93</v>
+        <v>1.98</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13651,10 +13651,10 @@
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF67" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13799,7 +13799,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -13996,7 +13996,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P69" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>2.32</v>
+        <v>2.37</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="R75" t="n">
-        <v>2.99</v>
+        <v>2.7</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>2.87</v>
+        <v>3.74</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="R76" t="n">
-        <v>2.3</v>
+        <v>1.88</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2.37</v>
+        <v>2.32</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="R77" t="n">
-        <v>2.7</v>
+        <v>2.99</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16409,10 +16409,10 @@
         <v>0</v>
       </c>
       <c r="AE81" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF81" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG81" t="n">
         <v>0</v>
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>4.02</v>
+        <v>0</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16606,10 +16606,10 @@
         <v>0</v>
       </c>
       <c r="AE82" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF82" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG82" t="n">
         <v>0</v>
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>4.51</v>
+        <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>4.51</v>
       </c>
       <c r="Q85" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R85" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>3.74</v>
+        <v>1.45</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.45</v>
+        <v>4.05</v>
       </c>
       <c r="R87" t="n">
-        <v>1.88</v>
+        <v>6.12</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17591,10 +17591,10 @@
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF87" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG87" t="n">
         <v>0</v>
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>1.45</v>
+        <v>1.74</v>
       </c>
       <c r="Q88" t="n">
-        <v>4.05</v>
+        <v>3.62</v>
       </c>
       <c r="R88" t="n">
-        <v>6.12</v>
+        <v>4.02</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17788,10 +17788,10 @@
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AF88" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AG88" t="n">
         <v>0</v>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>1.92</v>
+        <v>2.87</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.91</v>
+        <v>3.4</v>
       </c>
       <c r="R89" t="n">
-        <v>3.71</v>
+        <v>2.3</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18182,10 +18182,10 @@
         <v>0</v>
       </c>
       <c r="AE90" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF90" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG90" t="n">
         <v>0</v>
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1.26</v>
+        <v>1.92</v>
       </c>
       <c r="Q91" t="n">
-        <v>6.15</v>
+        <v>3.3</v>
       </c>
       <c r="R91" t="n">
-        <v>8.949999999999999</v>
+        <v>4.14</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>1.92</v>
+        <v>1.26</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.3</v>
+        <v>6.15</v>
       </c>
       <c r="R92" t="n">
-        <v>4.14</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>4.58</v>
+        <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18773,10 +18773,10 @@
         <v>0</v>
       </c>
       <c r="AE93" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF93" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG93" t="n">
         <v>0</v>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q96" t="n">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,10 +19364,10 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF96" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,22 +22423,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,22 +22620,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G127" t="n">

--- a/jogos_2026-05-01.xlsx
+++ b/jogos_2026-05-01.xlsx
@@ -1147,22 +1147,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3604,10 +3604,10 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>4.33</v>
+        <v>2.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="R17" t="n">
-        <v>1.73</v>
+        <v>3.25</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3801,10 +3801,10 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.72</v>
+        <v>2.1</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.98</v>
+        <v>1.65</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.2</v>
+        <v>4.33</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="R18" t="n">
-        <v>3.25</v>
+        <v>1.73</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -3998,10 +3998,10 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.1</v>
+        <v>1.72</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.65</v>
+        <v>1.98</v>
       </c>
       <c r="AG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>3.98</v>
+        <v>2.76</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.62</v>
+        <v>3.13</v>
       </c>
       <c r="R19" t="n">
-        <v>1.85</v>
+        <v>2.57</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4195,10 +4195,10 @@
         <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AG19" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.76</v>
+        <v>2.64</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.13</v>
+        <v>3.15</v>
       </c>
       <c r="R23" t="n">
-        <v>2.57</v>
+        <v>2.66</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -4983,10 +4983,10 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.66</v>
+        <v>2.1</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="AG23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5180,10 +5180,10 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>4.74</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5574,10 +5574,10 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5771,10 +5771,10 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>5.84</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.41</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>5.84</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Jamshedpur</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Jamshedpur</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2.58</v>
+        <v>3.76</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="R65" t="n">
-        <v>2.73</v>
+        <v>1.98</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>3.76</v>
+        <v>2.58</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="R67" t="n">
-        <v>1.98</v>
+        <v>2.73</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>3.74</v>
+        <v>1.74</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.45</v>
+        <v>3.62</v>
       </c>
       <c r="R76" t="n">
-        <v>1.88</v>
+        <v>4.02</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15424,10 +15424,10 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF76" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG76" t="n">
         <v>0</v>
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2.32</v>
+        <v>1.45</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.1</v>
+        <v>4.05</v>
       </c>
       <c r="R77" t="n">
-        <v>2.99</v>
+        <v>6.12</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15621,10 +15621,10 @@
         <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF77" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG77" t="n">
         <v>0</v>
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>2.1</v>
+        <v>3.74</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="R78" t="n">
-        <v>3.35</v>
+        <v>1.88</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1.42</v>
+        <v>4.51</v>
       </c>
       <c r="Q79" t="n">
-        <v>4.3</v>
+        <v>3.58</v>
       </c>
       <c r="R79" t="n">
-        <v>6.55</v>
+        <v>1.77</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1.92</v>
+        <v>1.42</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.91</v>
+        <v>4.3</v>
       </c>
       <c r="R80" t="n">
-        <v>3.71</v>
+        <v>6.55</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16409,10 +16409,10 @@
         <v>0</v>
       </c>
       <c r="AE81" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF81" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG81" t="n">
         <v>0</v>
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q82" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R82" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q83" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16803,10 +16803,10 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF83" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG83" t="n">
         <v>0</v>
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>4.51</v>
+        <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q86" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R86" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R87" t="n">
-        <v>6.12</v>
+        <v>0</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17591,10 +17591,10 @@
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF87" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG87" t="n">
         <v>0</v>
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>1.74</v>
+        <v>1.92</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.62</v>
+        <v>3.91</v>
       </c>
       <c r="R88" t="n">
-        <v>4.02</v>
+        <v>3.71</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17788,10 +17788,10 @@
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF88" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG88" t="n">
         <v>0</v>
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q90" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1.92</v>
+        <v>1.26</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.3</v>
+        <v>6.15</v>
       </c>
       <c r="R91" t="n">
-        <v>4.14</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>1.26</v>
+        <v>1.92</v>
       </c>
       <c r="Q92" t="n">
-        <v>6.15</v>
+        <v>3.3</v>
       </c>
       <c r="R92" t="n">
-        <v>8.949999999999999</v>
+        <v>4.14</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q95" t="n">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19167,10 +19167,10 @@
         <v>0</v>
       </c>
       <c r="AE95" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF95" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG95" t="n">
         <v>0</v>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Q96" t="n">
-        <v>4.58</v>
+        <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,10 +19364,10 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF96" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,22 +22029,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,22 +22423,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,22 +22620,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,22 +25378,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G127" t="n">

--- a/jogos_2026-05-01.xlsx
+++ b/jogos_2026-05-01.xlsx
@@ -950,22 +950,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1147,22 +1147,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Kuching FA</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kuching FA</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>4.74</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3604,10 +3604,10 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.2</v>
+        <v>1.59</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.25</v>
+        <v>3.98</v>
       </c>
       <c r="R17" t="n">
-        <v>3.25</v>
+        <v>5.35</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3801,10 +3801,10 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.1</v>
+        <v>1.78</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -3998,10 +3998,10 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4195,10 +4195,10 @@
         <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.98</v>
+        <v>3.94</v>
       </c>
       <c r="R20" t="n">
-        <v>5.35</v>
+        <v>4.74</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4392,10 +4392,10 @@
         <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.78</v>
+        <v>1.66</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AG20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>3.32</v>
+        <v>2.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.48</v>
+        <v>3.25</v>
       </c>
       <c r="R22" t="n">
-        <v>2.09</v>
+        <v>3.25</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.71</v>
+        <v>2.1</v>
       </c>
       <c r="AF22" t="n">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.64</v>
+        <v>3.32</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.15</v>
+        <v>3.48</v>
       </c>
       <c r="R23" t="n">
-        <v>2.66</v>
+        <v>2.09</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -4983,10 +4983,10 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.1</v>
+        <v>1.71</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AG23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3.98</v>
+        <v>2.76</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.62</v>
+        <v>3.13</v>
       </c>
       <c r="R24" t="n">
-        <v>1.85</v>
+        <v>2.57</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5180,10 +5180,10 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5574,10 +5574,10 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5771,10 +5771,10 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Jamshedpur</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>5.84</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.41</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>5.84</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Jamshedpur</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>3.76</v>
+        <v>2.34</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="R65" t="n">
-        <v>1.98</v>
+        <v>2.93</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13257,10 +13257,10 @@
         <v>0</v>
       </c>
       <c r="AE65" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF65" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>2.34</v>
+        <v>3.02</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="R66" t="n">
-        <v>2.93</v>
+        <v>2.15</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13454,10 +13454,10 @@
         <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF66" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>2.58</v>
+        <v>3.76</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="R67" t="n">
-        <v>2.73</v>
+        <v>1.98</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>3.02</v>
+        <v>2.58</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.6</v>
+        <v>3.12</v>
       </c>
       <c r="R68" t="n">
-        <v>2.15</v>
+        <v>2.73</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>1.74</v>
+        <v>2.87</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.62</v>
+        <v>3.4</v>
       </c>
       <c r="R76" t="n">
-        <v>4.02</v>
+        <v>2.3</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15424,10 +15424,10 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF76" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG76" t="n">
         <v>0</v>
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1.45</v>
+        <v>1.74</v>
       </c>
       <c r="Q77" t="n">
-        <v>4.05</v>
+        <v>3.62</v>
       </c>
       <c r="R77" t="n">
-        <v>6.12</v>
+        <v>4.02</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15621,10 +15621,10 @@
         <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AF77" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AG77" t="n">
         <v>0</v>
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>4.51</v>
+        <v>1.45</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.58</v>
+        <v>4.05</v>
       </c>
       <c r="R79" t="n">
-        <v>1.77</v>
+        <v>6.12</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16015,10 +16015,10 @@
         <v>0</v>
       </c>
       <c r="AE79" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF79" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG79" t="n">
         <v>0</v>
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>2.32</v>
+        <v>1.68</v>
       </c>
       <c r="Q82" t="n">
-        <v>3.1</v>
+        <v>3.62</v>
       </c>
       <c r="R82" t="n">
-        <v>2.99</v>
+        <v>4.4</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16606,10 +16606,10 @@
         <v>0</v>
       </c>
       <c r="AE82" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF82" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG82" t="n">
         <v>0</v>
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>1.68</v>
+        <v>1.42</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.62</v>
+        <v>4.3</v>
       </c>
       <c r="R83" t="n">
-        <v>4.4</v>
+        <v>6.55</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16803,10 +16803,10 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF83" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG83" t="n">
         <v>0</v>
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q84" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R84" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>2.37</v>
+        <v>4.51</v>
       </c>
       <c r="Q86" t="n">
-        <v>3.2</v>
+        <v>3.58</v>
       </c>
       <c r="R86" t="n">
-        <v>2.7</v>
+        <v>1.77</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="Q87" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R87" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>1.92</v>
+        <v>2.32</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.91</v>
+        <v>3.1</v>
       </c>
       <c r="R88" t="n">
-        <v>3.71</v>
+        <v>2.99</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>2.87</v>
+        <v>2.37</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="R89" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>6.15</v>
+        <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>8.949999999999999</v>
+        <v>0</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q93" t="n">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18773,10 +18773,10 @@
         <v>0</v>
       </c>
       <c r="AE93" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF93" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG93" t="n">
         <v>0</v>
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>1.5</v>
+        <v>1.26</v>
       </c>
       <c r="Q95" t="n">
-        <v>4.58</v>
+        <v>6.15</v>
       </c>
       <c r="R95" t="n">
-        <v>7.8</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19167,10 +19167,10 @@
         <v>0</v>
       </c>
       <c r="AE95" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF95" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG95" t="n">
         <v>0</v>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,22 +22029,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,22 +22817,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,22 +23999,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,22 +25378,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G127" t="n">

--- a/jogos_2026-05-01.xlsx
+++ b/jogos_2026-05-01.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3604,10 +3604,10 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3801,10 +3801,10 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -3998,10 +3998,10 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.94</v>
+        <v>3.98</v>
       </c>
       <c r="R20" t="n">
-        <v>4.74</v>
+        <v>5.35</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4392,10 +4392,10 @@
         <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.66</v>
+        <v>1.78</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AG20" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.2</v>
+        <v>4.33</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="R22" t="n">
-        <v>3.25</v>
+        <v>1.73</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.1</v>
+        <v>1.72</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.65</v>
+        <v>1.98</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>3.32</v>
+        <v>3.98</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.48</v>
+        <v>3.62</v>
       </c>
       <c r="R23" t="n">
-        <v>2.09</v>
+        <v>1.85</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -4983,10 +4983,10 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AF23" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AG23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.76</v>
+        <v>3.32</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.13</v>
+        <v>3.48</v>
       </c>
       <c r="R24" t="n">
-        <v>2.57</v>
+        <v>2.09</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5180,10 +5180,10 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3.98</v>
+        <v>2.76</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.62</v>
+        <v>3.13</v>
       </c>
       <c r="R25" t="n">
-        <v>1.85</v>
+        <v>2.57</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5574,10 +5574,10 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Jamshedpur</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Jamshedpur</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>5.84</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>4.41</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>5.84</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>3.76</v>
+        <v>2.58</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="R67" t="n">
-        <v>1.98</v>
+        <v>2.73</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13799,17 +13799,17 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P68" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -13996,17 +13996,17 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,22 +14346,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>2.87</v>
+        <v>1.74</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.4</v>
+        <v>3.62</v>
       </c>
       <c r="R76" t="n">
-        <v>2.3</v>
+        <v>4.02</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15424,10 +15424,10 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF76" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG76" t="n">
         <v>0</v>
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1.74</v>
+        <v>2.87</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.62</v>
+        <v>3.4</v>
       </c>
       <c r="R77" t="n">
-        <v>4.02</v>
+        <v>2.3</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15621,10 +15621,10 @@
         <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF77" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG77" t="n">
         <v>0</v>
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>4.51</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="Q79" t="n">
-        <v>4.05</v>
+        <v>4.3</v>
       </c>
       <c r="R79" t="n">
-        <v>6.12</v>
+        <v>6.55</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16015,10 +16015,10 @@
         <v>0</v>
       </c>
       <c r="AE79" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF79" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG79" t="n">
         <v>0</v>
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1.92</v>
+        <v>2.37</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.91</v>
+        <v>3.2</v>
       </c>
       <c r="R81" t="n">
-        <v>3.71</v>
+        <v>2.7</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>1.68</v>
+        <v>1.45</v>
       </c>
       <c r="Q82" t="n">
-        <v>3.62</v>
+        <v>4.05</v>
       </c>
       <c r="R82" t="n">
-        <v>4.4</v>
+        <v>6.12</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>1.42</v>
+        <v>1.74</v>
       </c>
       <c r="Q83" t="n">
-        <v>4.3</v>
+        <v>3.52</v>
       </c>
       <c r="R83" t="n">
-        <v>6.55</v>
+        <v>4.17</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16803,10 +16803,10 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF83" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG83" t="n">
         <v>0</v>
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>4.51</v>
+        <v>1.68</v>
       </c>
       <c r="Q86" t="n">
-        <v>3.58</v>
+        <v>3.62</v>
       </c>
       <c r="R86" t="n">
-        <v>1.77</v>
+        <v>4.4</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17394,10 +17394,10 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF86" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG86" t="n">
         <v>0</v>
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>3.74</v>
+        <v>2.31</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.45</v>
+        <v>3.16</v>
       </c>
       <c r="R87" t="n">
-        <v>1.88</v>
+        <v>2.86</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>2.32</v>
+        <v>3.74</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="R88" t="n">
-        <v>2.99</v>
+        <v>1.88</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q90" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q91" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Q92" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>4.58</v>
+        <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18773,10 +18773,10 @@
         <v>0</v>
       </c>
       <c r="AE93" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF93" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG93" t="n">
         <v>0</v>
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Q95" t="n">
-        <v>6.15</v>
+        <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>8.949999999999999</v>
+        <v>0</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q96" t="n">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,10 +19364,10 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF96" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,22 +22817,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,22 +23999,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,22 +24787,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="G127" t="n">

--- a/jogos_2026-05-01.xlsx
+++ b/jogos_2026-05-01.xlsx
@@ -950,22 +950,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2028,10 +2028,10 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3801,10 +3801,10 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.66</v>
+        <v>2.76</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.94</v>
+        <v>3.13</v>
       </c>
       <c r="R18" t="n">
-        <v>4.74</v>
+        <v>2.57</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4195,10 +4195,10 @@
         <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG19" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>4.33</v>
+        <v>2.64</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.8</v>
+        <v>3.15</v>
       </c>
       <c r="R22" t="n">
-        <v>1.73</v>
+        <v>2.66</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.72</v>
+        <v>2.1</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.98</v>
+        <v>1.65</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>3.98</v>
+        <v>3.32</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.62</v>
+        <v>3.48</v>
       </c>
       <c r="R23" t="n">
-        <v>1.85</v>
+        <v>2.09</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -4983,10 +4983,10 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AG23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5180,10 +5180,10 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.76</v>
+        <v>3.98</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.13</v>
+        <v>3.62</v>
       </c>
       <c r="R25" t="n">
-        <v>2.57</v>
+        <v>1.85</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.64</v>
+        <v>2.23</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="R27" t="n">
-        <v>2.66</v>
+        <v>3.26</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5771,10 +5771,10 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Jamshedpur</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Jamshedpur</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>5.84</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>5.84</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>4.41</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2.34</v>
+        <v>3.02</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="R65" t="n">
-        <v>2.93</v>
+        <v>2.15</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13257,10 +13257,10 @@
         <v>0</v>
       </c>
       <c r="AE65" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF65" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>3.02</v>
+        <v>2.58</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.6</v>
+        <v>3.12</v>
       </c>
       <c r="R66" t="n">
-        <v>2.15</v>
+        <v>2.73</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>2.58</v>
+        <v>2.34</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
       <c r="R67" t="n">
-        <v>2.73</v>
+        <v>2.93</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13651,10 +13651,10 @@
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF67" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG67" t="n">
         <v>0</v>
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,22 +14346,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>2.32</v>
+        <v>2</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.1</v>
+        <v>3.54</v>
       </c>
       <c r="R75" t="n">
-        <v>2.99</v>
+        <v>3.52</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>4.02</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15424,10 +15424,10 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF76" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG76" t="n">
         <v>0</v>
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2.87</v>
+        <v>2.16</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R77" t="n">
-        <v>2.3</v>
+        <v>3.14</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15621,10 +15621,10 @@
         <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF77" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG77" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1.42</v>
+        <v>1.92</v>
       </c>
       <c r="Q79" t="n">
-        <v>4.3</v>
+        <v>3.91</v>
       </c>
       <c r="R79" t="n">
-        <v>6.55</v>
+        <v>3.71</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>2.1</v>
+        <v>2.87</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="R80" t="n">
-        <v>3.35</v>
+        <v>2.3</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>2.37</v>
+        <v>3.74</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="R81" t="n">
-        <v>2.7</v>
+        <v>1.88</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>1.45</v>
+        <v>2.37</v>
       </c>
       <c r="Q82" t="n">
-        <v>4.05</v>
+        <v>3.2</v>
       </c>
       <c r="R82" t="n">
-        <v>6.12</v>
+        <v>2.7</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16606,10 +16606,10 @@
         <v>0</v>
       </c>
       <c r="AE82" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF82" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG82" t="n">
         <v>0</v>
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>1.74</v>
+        <v>2.32</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.52</v>
+        <v>3.1</v>
       </c>
       <c r="R83" t="n">
-        <v>4.17</v>
+        <v>2.99</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16803,10 +16803,10 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF83" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG83" t="n">
         <v>0</v>
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Q84" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R84" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q85" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R85" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>3.74</v>
+        <v>1.45</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.45</v>
+        <v>4.05</v>
       </c>
       <c r="R88" t="n">
-        <v>1.88</v>
+        <v>6.12</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17788,10 +17788,10 @@
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF88" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG88" t="n">
         <v>0</v>
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q89" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R89" t="n">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -17985,10 +17985,10 @@
         <v>0</v>
       </c>
       <c r="AE89" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF89" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG89" t="n">
         <v>0</v>
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1.92</v>
+        <v>1.74</v>
       </c>
       <c r="Q90" t="n">
-        <v>3.91</v>
+        <v>3.52</v>
       </c>
       <c r="R90" t="n">
-        <v>3.71</v>
+        <v>4.17</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18182,10 +18182,10 @@
         <v>0</v>
       </c>
       <c r="AE90" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF90" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG90" t="n">
         <v>0</v>
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1.92</v>
+        <v>1.26</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.3</v>
+        <v>6.15</v>
       </c>
       <c r="R91" t="n">
-        <v>4.14</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>6.15</v>
+        <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>8.949999999999999</v>
+        <v>0</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q93" t="n">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18773,10 +18773,10 @@
         <v>0</v>
       </c>
       <c r="AE93" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF93" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG93" t="n">
         <v>0</v>
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Q96" t="n">
-        <v>4.58</v>
+        <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,10 +19364,10 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF96" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,22 +24787,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G127" t="n">

--- a/jogos_2026-05-01.xlsx
+++ b/jogos_2026-05-01.xlsx
@@ -950,22 +950,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2028,10 +2028,10 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kuching FA</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Kuching FA</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.2</v>
+        <v>4.33</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="R16" t="n">
-        <v>3.25</v>
+        <v>1.73</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3604,10 +3604,10 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.1</v>
+        <v>1.72</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.65</v>
+        <v>1.98</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.66</v>
+        <v>2.76</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.94</v>
+        <v>3.13</v>
       </c>
       <c r="R17" t="n">
-        <v>4.74</v>
+        <v>2.57</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -3998,10 +3998,10 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>4.33</v>
+        <v>1.59</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.8</v>
+        <v>3.98</v>
       </c>
       <c r="R19" t="n">
-        <v>1.73</v>
+        <v>5.35</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4195,10 +4195,10 @@
         <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="AG19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4392,10 +4392,10 @@
         <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.64</v>
+        <v>3.98</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.15</v>
+        <v>3.62</v>
       </c>
       <c r="R22" t="n">
-        <v>2.66</v>
+        <v>1.85</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -4983,10 +4983,10 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5180,10 +5180,10 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3.98</v>
+        <v>2.64</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.62</v>
+        <v>3.15</v>
       </c>
       <c r="R25" t="n">
-        <v>1.85</v>
+        <v>2.66</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5574,10 +5574,10 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="R27" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5771,10 +5771,10 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Jamshedpur</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.73</v>
+        <v>5.84</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.16</v>
+        <v>4.41</v>
       </c>
       <c r="R29" t="n">
-        <v>2.34</v>
+        <v>1.62</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>5.84</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.41</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Jamshedpur</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13405,17 +13405,17 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P66" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>2.34</v>
+        <v>2.58</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.25</v>
+        <v>3.12</v>
       </c>
       <c r="R67" t="n">
-        <v>2.93</v>
+        <v>2.73</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13651,10 +13651,10 @@
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF67" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG67" t="n">
         <v>0</v>
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13799,17 +13799,17 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13848,10 +13848,10 @@
         <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF68" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG68" t="n">
         <v>0</v>
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>2</v>
+        <v>1.42</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.54</v>
+        <v>4.3</v>
       </c>
       <c r="R75" t="n">
-        <v>3.52</v>
+        <v>6.55</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="R77" t="n">
-        <v>3.14</v>
+        <v>3.35</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15621,10 +15621,10 @@
         <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF77" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>4.51</v>
+        <v>1.68</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.58</v>
+        <v>3.62</v>
       </c>
       <c r="R78" t="n">
-        <v>1.77</v>
+        <v>4.4</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15818,10 +15818,10 @@
         <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF78" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1.92</v>
+        <v>2.32</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.91</v>
+        <v>3.1</v>
       </c>
       <c r="R79" t="n">
-        <v>3.71</v>
+        <v>2.99</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>2.87</v>
+        <v>2</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.4</v>
+        <v>3.54</v>
       </c>
       <c r="R80" t="n">
-        <v>2.3</v>
+        <v>3.52</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>3.74</v>
+        <v>4.51</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.45</v>
+        <v>3.58</v>
       </c>
       <c r="R81" t="n">
-        <v>1.88</v>
+        <v>1.77</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>2.37</v>
+        <v>2.16</v>
       </c>
       <c r="Q82" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="R82" t="n">
-        <v>2.7</v>
+        <v>3.14</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16606,10 +16606,10 @@
         <v>0</v>
       </c>
       <c r="AE82" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF82" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG82" t="n">
         <v>0</v>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>2.32</v>
+        <v>2.87</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="R83" t="n">
-        <v>2.99</v>
+        <v>2.3</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>1.42</v>
+        <v>1.74</v>
       </c>
       <c r="Q84" t="n">
-        <v>4.3</v>
+        <v>3.62</v>
       </c>
       <c r="R84" t="n">
-        <v>6.55</v>
+        <v>4.02</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17000,10 +17000,10 @@
         <v>0</v>
       </c>
       <c r="AE84" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF84" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG84" t="n">
         <v>0</v>
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>2.1</v>
+        <v>2.31</v>
       </c>
       <c r="Q85" t="n">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="R85" t="n">
-        <v>3.35</v>
+        <v>2.86</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>1.68</v>
+        <v>1.92</v>
       </c>
       <c r="Q86" t="n">
-        <v>3.62</v>
+        <v>3.91</v>
       </c>
       <c r="R86" t="n">
-        <v>4.4</v>
+        <v>3.71</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17394,10 +17394,10 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF86" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG86" t="n">
         <v>0</v>
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>2.31</v>
+        <v>2.37</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="R87" t="n">
-        <v>2.86</v>
+        <v>2.7</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>1.45</v>
+        <v>1.74</v>
       </c>
       <c r="Q88" t="n">
-        <v>4.05</v>
+        <v>3.52</v>
       </c>
       <c r="R88" t="n">
-        <v>6.12</v>
+        <v>4.17</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17788,10 +17788,10 @@
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="AF88" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AG88" t="n">
         <v>0</v>
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>1.74</v>
+        <v>1.45</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.62</v>
+        <v>4.05</v>
       </c>
       <c r="R89" t="n">
-        <v>4.02</v>
+        <v>6.12</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -17985,10 +17985,10 @@
         <v>0</v>
       </c>
       <c r="AE89" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AF89" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AG89" t="n">
         <v>0</v>
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1.74</v>
+        <v>3.74</v>
       </c>
       <c r="Q90" t="n">
-        <v>3.52</v>
+        <v>3.45</v>
       </c>
       <c r="R90" t="n">
-        <v>4.17</v>
+        <v>1.88</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18182,10 +18182,10 @@
         <v>0</v>
       </c>
       <c r="AE90" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF90" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG90" t="n">
         <v>0</v>
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>6.15</v>
+        <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>8.949999999999999</v>
+        <v>0</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>1.5</v>
+        <v>1.92</v>
       </c>
       <c r="Q93" t="n">
-        <v>4.58</v>
+        <v>3.3</v>
       </c>
       <c r="R93" t="n">
-        <v>7.8</v>
+        <v>4.14</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18773,10 +18773,10 @@
         <v>0</v>
       </c>
       <c r="AE93" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF93" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG93" t="n">
         <v>0</v>
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>1.92</v>
+        <v>1.26</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.3</v>
+        <v>6.15</v>
       </c>
       <c r="R94" t="n">
-        <v>4.14</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q96" t="n">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,10 +19364,10 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF96" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,22 +24196,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25181,22 +25181,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G127" t="n">

--- a/jogos_2026-05-01.xlsx
+++ b/jogos_2026-05-01.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI128"/>
+  <dimension ref="A1:BI130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -950,22 +950,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2028,10 +2028,10 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Kuching FA</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kuching FA</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>4.33</v>
+        <v>1.66</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.8</v>
+        <v>3.94</v>
       </c>
       <c r="R16" t="n">
-        <v>1.73</v>
+        <v>4.74</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3604,10 +3604,10 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.76</v>
+        <v>1.59</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.13</v>
+        <v>3.98</v>
       </c>
       <c r="R17" t="n">
-        <v>2.57</v>
+        <v>5.35</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3801,10 +3801,10 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.66</v>
+        <v>1.78</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4195,10 +4195,10 @@
         <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4392,10 +4392,10 @@
         <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.23</v>
+        <v>2.64</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="R21" t="n">
-        <v>3.26</v>
+        <v>2.66</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>3.98</v>
+        <v>4.33</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.62</v>
+        <v>3.8</v>
       </c>
       <c r="R22" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -4983,10 +4983,10 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>4.74</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5180,10 +5180,10 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.64</v>
+        <v>3.32</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.15</v>
+        <v>3.48</v>
       </c>
       <c r="R25" t="n">
-        <v>2.66</v>
+        <v>2.09</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.1</v>
+        <v>1.71</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>3.32</v>
+        <v>2.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.48</v>
+        <v>3.25</v>
       </c>
       <c r="R26" t="n">
-        <v>2.09</v>
+        <v>3.25</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5574,10 +5574,10 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.71</v>
+        <v>2.1</v>
       </c>
       <c r="AF26" t="n">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AG26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.2</v>
+        <v>2.76</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.25</v>
+        <v>3.13</v>
       </c>
       <c r="R27" t="n">
-        <v>3.25</v>
+        <v>2.57</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5771,10 +5771,10 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.1</v>
+        <v>1.66</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Jamshedpur</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Jamshedpur</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8825,27 +8825,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9013,7 +9013,7 @@
         <v>0</v>
       </c>
       <c r="BI43" s="3" t="n">
-        <v>46143.46875</v>
+        <v>46143.45833333334</v>
       </c>
     </row>
     <row r="44">
@@ -9022,12 +9022,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9210,7 +9210,7 @@
         <v>0</v>
       </c>
       <c r="BI44" s="3" t="n">
-        <v>46143.47916666666</v>
+        <v>46143.46875</v>
       </c>
     </row>
     <row r="45">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9416,12 +9416,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9604,7 +9604,7 @@
         <v>0</v>
       </c>
       <c r="BI46" s="3" t="n">
-        <v>46143.5</v>
+        <v>46143.47916666666</v>
       </c>
     </row>
     <row r="47">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10992,12 +10992,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11180,7 +11180,7 @@
         <v>0</v>
       </c>
       <c r="BI54" s="3" t="n">
-        <v>46143.52083333334</v>
+        <v>46143.5</v>
       </c>
     </row>
     <row r="55">
@@ -11189,12 +11189,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11377,7 +11377,7 @@
         <v>0</v>
       </c>
       <c r="BI55" s="3" t="n">
-        <v>46143.54166666666</v>
+        <v>46143.52083333334</v>
       </c>
     </row>
     <row r="56">
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11780,27 +11780,27 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11968,7 +11968,7 @@
         <v>0</v>
       </c>
       <c r="BI58" s="3" t="n">
-        <v>46143.5625</v>
+        <v>46143.54166666666</v>
       </c>
     </row>
     <row r="59">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12371,12 +12371,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12559,7 +12559,7 @@
         <v>0</v>
       </c>
       <c r="BI61" s="3" t="n">
-        <v>46143.58333333334</v>
+        <v>46143.5625</v>
       </c>
     </row>
     <row r="62">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13159,12 +13159,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13347,7 +13347,7 @@
         <v>0</v>
       </c>
       <c r="BI65" s="3" t="n">
-        <v>46143.60416666666</v>
+        <v>46143.58333333334</v>
       </c>
     </row>
     <row r="66">
@@ -13356,12 +13356,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13405,7 +13405,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P66" t="n">
@@ -13544,7 +13544,7 @@
         <v>0</v>
       </c>
       <c r="BI66" s="3" t="n">
-        <v>46143.60416666666</v>
+        <v>46143.58333333334</v>
       </c>
     </row>
     <row r="67">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>2.58</v>
+        <v>2.34</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
       <c r="R67" t="n">
-        <v>2.73</v>
+        <v>2.93</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13651,10 +13651,10 @@
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF67" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>2.34</v>
+        <v>3.76</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="R68" t="n">
-        <v>2.93</v>
+        <v>1.98</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13848,10 +13848,10 @@
         <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF68" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -13996,17 +13996,17 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P69" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14144,12 +14144,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14332,7 +14332,7 @@
         <v>0</v>
       </c>
       <c r="BI70" s="3" t="n">
-        <v>46143.625</v>
+        <v>46143.60416666666</v>
       </c>
     </row>
     <row r="71">
@@ -14341,27 +14341,27 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14529,7 +14529,7 @@
         <v>0</v>
       </c>
       <c r="BI71" s="3" t="n">
-        <v>46143.625</v>
+        <v>46143.60416666666</v>
       </c>
     </row>
     <row r="72">
@@ -14538,27 +14538,27 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14726,7 +14726,7 @@
         <v>0</v>
       </c>
       <c r="BI72" s="3" t="n">
-        <v>46143.63541666666</v>
+        <v>46143.625</v>
       </c>
     </row>
     <row r="73">
@@ -14735,12 +14735,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14923,7 +14923,7 @@
         <v>0</v>
       </c>
       <c r="BI73" s="3" t="n">
-        <v>46143.64583333334</v>
+        <v>46143.625</v>
       </c>
     </row>
     <row r="74">
@@ -14932,12 +14932,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15120,7 +15120,7 @@
         <v>0</v>
       </c>
       <c r="BI74" s="3" t="n">
-        <v>46143.64583333334</v>
+        <v>46143.63541666666</v>
       </c>
     </row>
     <row r="75">
@@ -15129,12 +15129,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15317,7 +15317,7 @@
         <v>0</v>
       </c>
       <c r="BI75" s="3" t="n">
-        <v>46143.65625</v>
+        <v>46143.64583333334</v>
       </c>
     </row>
     <row r="76">
@@ -15326,12 +15326,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15514,7 +15514,7 @@
         <v>0</v>
       </c>
       <c r="BI76" s="3" t="n">
-        <v>46143.65625</v>
+        <v>46143.64583333334</v>
       </c>
     </row>
     <row r="77">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2.1</v>
+        <v>2.37</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="R77" t="n">
-        <v>3.35</v>
+        <v>2.7</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>1.68</v>
+        <v>2.87</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.62</v>
+        <v>3.4</v>
       </c>
       <c r="R78" t="n">
-        <v>4.4</v>
+        <v>2.3</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15818,10 +15818,10 @@
         <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF78" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG78" t="n">
         <v>0</v>
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>2.32</v>
+        <v>1.45</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.1</v>
+        <v>4.05</v>
       </c>
       <c r="R79" t="n">
-        <v>2.99</v>
+        <v>6.12</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16015,10 +16015,10 @@
         <v>0</v>
       </c>
       <c r="AE79" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF79" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.54</v>
+        <v>3.62</v>
       </c>
       <c r="R80" t="n">
-        <v>3.52</v>
+        <v>4.02</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16212,10 +16212,10 @@
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF80" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG80" t="n">
         <v>0</v>
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>4.51</v>
+        <v>2.1</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.58</v>
+        <v>3.15</v>
       </c>
       <c r="R81" t="n">
-        <v>1.77</v>
+        <v>3.35</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>2.16</v>
+        <v>3.74</v>
       </c>
       <c r="Q82" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="R82" t="n">
-        <v>3.14</v>
+        <v>1.88</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16606,10 +16606,10 @@
         <v>0</v>
       </c>
       <c r="AE82" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF82" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG82" t="n">
         <v>0</v>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>2.87</v>
+        <v>1.92</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.4</v>
+        <v>3.91</v>
       </c>
       <c r="R83" t="n">
-        <v>2.3</v>
+        <v>3.71</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="Q84" t="n">
         <v>3.62</v>
       </c>
       <c r="R84" t="n">
-        <v>4.02</v>
+        <v>4.4</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17000,10 +17000,10 @@
         <v>0</v>
       </c>
       <c r="AE84" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AF84" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AG84" t="n">
         <v>0</v>
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>1.92</v>
+        <v>4.51</v>
       </c>
       <c r="Q86" t="n">
-        <v>3.91</v>
+        <v>3.58</v>
       </c>
       <c r="R86" t="n">
-        <v>3.71</v>
+        <v>1.77</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>2.37</v>
+        <v>1.42</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="R87" t="n">
-        <v>2.7</v>
+        <v>6.55</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>1.45</v>
+        <v>2.31</v>
       </c>
       <c r="Q89" t="n">
-        <v>4.05</v>
+        <v>3.16</v>
       </c>
       <c r="R89" t="n">
-        <v>6.12</v>
+        <v>2.86</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -17985,10 +17985,10 @@
         <v>0</v>
       </c>
       <c r="AE89" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF89" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG89" t="n">
         <v>0</v>
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>3.74</v>
+        <v>2.16</v>
       </c>
       <c r="Q90" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="R90" t="n">
-        <v>1.88</v>
+        <v>3.14</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18182,10 +18182,10 @@
         <v>0</v>
       </c>
       <c r="AE90" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF90" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG90" t="n">
         <v>0</v>
@@ -18281,27 +18281,27 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q91" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18469,7 +18469,7 @@
         <v>0</v>
       </c>
       <c r="BI91" s="3" t="n">
-        <v>46143.66666666666</v>
+        <v>46143.65625</v>
       </c>
     </row>
     <row r="92">
@@ -18478,12 +18478,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q92" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18666,7 +18666,7 @@
         <v>0</v>
       </c>
       <c r="BI92" s="3" t="n">
-        <v>46143.66666666666</v>
+        <v>46143.65625</v>
       </c>
     </row>
     <row r="93">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>1.92</v>
+        <v>1.26</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.3</v>
+        <v>6.15</v>
       </c>
       <c r="R93" t="n">
-        <v>4.14</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>6.15</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>8.949999999999999</v>
+        <v>0</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Q96" t="n">
-        <v>4.58</v>
+        <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,10 +19364,10 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF96" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -19463,12 +19463,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q97" t="n">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="R97" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19561,10 +19561,10 @@
         <v>0</v>
       </c>
       <c r="AE97" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF97" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG97" t="n">
         <v>0</v>
@@ -19651,7 +19651,7 @@
         <v>0</v>
       </c>
       <c r="BI97" s="3" t="n">
-        <v>46143.6875</v>
+        <v>46143.66666666666</v>
       </c>
     </row>
     <row r="98">
@@ -19660,12 +19660,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q98" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19848,7 +19848,7 @@
         <v>0</v>
       </c>
       <c r="BI98" s="3" t="n">
-        <v>46143.76041666666</v>
+        <v>46143.66666666666</v>
       </c>
     </row>
     <row r="99">
@@ -19857,27 +19857,27 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20045,7 +20045,7 @@
         <v>0</v>
       </c>
       <c r="BI99" s="3" t="n">
-        <v>46143.77083333334</v>
+        <v>46143.6875</v>
       </c>
     </row>
     <row r="100">
@@ -20054,12 +20054,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20242,7 +20242,7 @@
         <v>0</v>
       </c>
       <c r="BI100" s="3" t="n">
-        <v>46143.85416666666</v>
+        <v>46143.76041666666</v>
       </c>
     </row>
     <row r="101">
@@ -20251,27 +20251,27 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20439,7 +20439,7 @@
         <v>0</v>
       </c>
       <c r="BI101" s="3" t="n">
-        <v>46143.875</v>
+        <v>46143.77083333334</v>
       </c>
     </row>
     <row r="102">
@@ -20448,27 +20448,27 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20636,7 +20636,7 @@
         <v>0</v>
       </c>
       <c r="BI102" s="3" t="n">
-        <v>46143.875</v>
+        <v>46143.85416666666</v>
       </c>
     </row>
     <row r="103">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,22 +23014,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,22 +23999,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,22 +24196,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25181,22 +25181,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25570,27 +25570,27 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25758,6 +25758,400 @@
         <v>0</v>
       </c>
       <c r="BI128" s="3" t="n">
+        <v>46143.875</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Velež</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Radnik Bijeljina</t>
+        </is>
+      </c>
+      <c r="G129" t="n">
+        <v>0</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0</v>
+      </c>
+      <c r="M129" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N129" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P129" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI129" s="3" t="n">
+        <v>46143.875</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>LA Galaxy II</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>San Jose Earthquakes II</t>
+        </is>
+      </c>
+      <c r="G130" t="n">
+        <v>0</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0</v>
+      </c>
+      <c r="M130" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N130" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P130" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI130" s="3" t="n">
         <v>46143.95833333334</v>
       </c>
     </row>

--- a/jogos_2026-05-01.xlsx
+++ b/jogos_2026-05-01.xlsx
@@ -1147,22 +1147,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2028,10 +2028,10 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.66</v>
+        <v>2.64</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.94</v>
+        <v>3.15</v>
       </c>
       <c r="R16" t="n">
-        <v>4.74</v>
+        <v>2.66</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3604,10 +3604,10 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.66</v>
+        <v>2.1</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.98</v>
+        <v>3.94</v>
       </c>
       <c r="R17" t="n">
-        <v>5.35</v>
+        <v>4.74</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3801,10 +3801,10 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.78</v>
+        <v>1.66</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -3998,10 +3998,10 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4195,10 +4195,10 @@
         <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.23</v>
+        <v>4.33</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="R20" t="n">
-        <v>3.26</v>
+        <v>1.73</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4392,10 +4392,10 @@
         <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.15</v>
+        <v>1.72</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.61</v>
+        <v>1.98</v>
       </c>
       <c r="AG20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.64</v>
+        <v>3.32</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.15</v>
+        <v>3.48</v>
       </c>
       <c r="R21" t="n">
-        <v>2.66</v>
+        <v>2.09</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.1</v>
+        <v>1.71</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>4.33</v>
+        <v>1.59</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.8</v>
+        <v>3.98</v>
       </c>
       <c r="R22" t="n">
-        <v>1.73</v>
+        <v>5.35</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,55 +4938,55 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>3.98</v>
+        <v>2.29</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.62</v>
+        <v>3.14</v>
       </c>
       <c r="R23" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AF23" t="n">
         <v>1.85</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W23" t="n">
-        <v>0</v>
-      </c>
-      <c r="X23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.9</v>
       </c>
       <c r="AG23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.2</v>
+        <v>2.76</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.25</v>
+        <v>3.13</v>
       </c>
       <c r="R26" t="n">
-        <v>3.25</v>
+        <v>2.57</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5574,10 +5574,10 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.1</v>
+        <v>1.66</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="AG26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.76</v>
+        <v>2.23</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.13</v>
+        <v>3.2</v>
       </c>
       <c r="R27" t="n">
-        <v>2.57</v>
+        <v>3.26</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5771,10 +5771,10 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.66</v>
+        <v>2.15</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.05</v>
+        <v>1.61</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>5.84</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.41</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Jamshedpur</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>5.84</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Jamshedpur</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>2.34</v>
+        <v>3.02</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="R67" t="n">
-        <v>2.93</v>
+        <v>2.15</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13651,10 +13651,10 @@
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF67" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13799,17 +13799,17 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P68" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -13996,17 +13996,17 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>3.02</v>
+        <v>2.34</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="R70" t="n">
-        <v>2.15</v>
+        <v>2.93</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14242,10 +14242,10 @@
         <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF70" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG70" t="n">
         <v>0</v>
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2.37</v>
+        <v>4.51</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.2</v>
+        <v>3.58</v>
       </c>
       <c r="R77" t="n">
-        <v>2.7</v>
+        <v>1.77</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>2.87</v>
+        <v>1.74</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.4</v>
+        <v>3.62</v>
       </c>
       <c r="R78" t="n">
-        <v>2.3</v>
+        <v>4.02</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15818,10 +15818,10 @@
         <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF78" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG78" t="n">
         <v>0</v>
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1.45</v>
+        <v>1.74</v>
       </c>
       <c r="Q79" t="n">
-        <v>4.05</v>
+        <v>3.52</v>
       </c>
       <c r="R79" t="n">
-        <v>6.12</v>
+        <v>4.17</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16015,10 +16015,10 @@
         <v>0</v>
       </c>
       <c r="AE79" t="n">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="AF79" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AG79" t="n">
         <v>0</v>
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="Q80" t="n">
         <v>3.62</v>
       </c>
       <c r="R80" t="n">
-        <v>4.02</v>
+        <v>4.4</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16212,10 +16212,10 @@
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AF80" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AG80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>2.1</v>
+        <v>2.87</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="R81" t="n">
-        <v>3.35</v>
+        <v>2.3</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>3.74</v>
+        <v>1.92</v>
       </c>
       <c r="Q82" t="n">
-        <v>3.45</v>
+        <v>3.91</v>
       </c>
       <c r="R82" t="n">
-        <v>1.88</v>
+        <v>3.71</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>1.92</v>
+        <v>2.16</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.91</v>
+        <v>3.5</v>
       </c>
       <c r="R83" t="n">
-        <v>3.71</v>
+        <v>3.14</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16803,10 +16803,10 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF83" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG83" t="n">
         <v>0</v>
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>1.68</v>
+        <v>2.31</v>
       </c>
       <c r="Q84" t="n">
-        <v>3.62</v>
+        <v>3.16</v>
       </c>
       <c r="R84" t="n">
-        <v>4.4</v>
+        <v>2.86</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17000,10 +17000,10 @@
         <v>0</v>
       </c>
       <c r="AE84" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF84" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG84" t="n">
         <v>0</v>
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>4.51</v>
+        <v>1.45</v>
       </c>
       <c r="Q86" t="n">
-        <v>3.58</v>
+        <v>4.05</v>
       </c>
       <c r="R86" t="n">
-        <v>1.77</v>
+        <v>6.12</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17394,10 +17394,10 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF86" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG86" t="n">
         <v>0</v>
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>1.42</v>
+        <v>2</v>
       </c>
       <c r="Q87" t="n">
-        <v>4.3</v>
+        <v>3.54</v>
       </c>
       <c r="R87" t="n">
-        <v>6.55</v>
+        <v>3.52</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>1.74</v>
+        <v>3.74</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.52</v>
+        <v>3.45</v>
       </c>
       <c r="R88" t="n">
-        <v>4.17</v>
+        <v>1.88</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17788,10 +17788,10 @@
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF88" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG88" t="n">
         <v>0</v>
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>2.31</v>
+        <v>2.1</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="R89" t="n">
-        <v>2.86</v>
+        <v>3.35</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>2.16</v>
+        <v>1.42</v>
       </c>
       <c r="Q90" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="R90" t="n">
-        <v>3.14</v>
+        <v>6.55</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18182,10 +18182,10 @@
         <v>0</v>
       </c>
       <c r="AE90" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF90" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG90" t="n">
         <v>0</v>
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>2</v>
+        <v>2.32</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.54</v>
+        <v>3.1</v>
       </c>
       <c r="R91" t="n">
-        <v>3.52</v>
+        <v>2.99</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>2.32</v>
+        <v>2.37</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="R92" t="n">
-        <v>2.99</v>
+        <v>2.7</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>6.15</v>
+        <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>8.949999999999999</v>
+        <v>0</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -18970,10 +18970,10 @@
         <v>0</v>
       </c>
       <c r="AE94" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF94" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG94" t="n">
         <v>0</v>
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q95" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Q96" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Q97" t="n">
-        <v>4.58</v>
+        <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19561,10 +19561,10 @@
         <v>0</v>
       </c>
       <c r="AE97" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF97" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG97" t="n">
         <v>0</v>
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q98" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,22 +22817,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,22 +23014,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G129" t="n">

--- a/jogos_2026-05-01.xlsx
+++ b/jogos_2026-05-01.xlsx
@@ -950,22 +950,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1147,22 +1147,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1240,10 +1240,10 @@
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kuching FA</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Kuching FA</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.64</v>
+        <v>1.66</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.15</v>
+        <v>3.94</v>
       </c>
       <c r="R16" t="n">
-        <v>2.66</v>
+        <v>4.74</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3604,10 +3604,10 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.1</v>
+        <v>1.66</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.66</v>
+        <v>2.29</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.94</v>
+        <v>3.14</v>
       </c>
       <c r="R17" t="n">
-        <v>4.74</v>
+        <v>3.21</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3801,10 +3801,10 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.66</v>
+        <v>1.83</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.2</v>
+        <v>2.76</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.25</v>
+        <v>3.13</v>
       </c>
       <c r="R18" t="n">
-        <v>3.25</v>
+        <v>2.57</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -3998,10 +3998,10 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.1</v>
+        <v>1.66</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="AG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>3.98</v>
+        <v>3.32</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.62</v>
+        <v>3.48</v>
       </c>
       <c r="R19" t="n">
-        <v>1.85</v>
+        <v>2.09</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4195,10 +4195,10 @@
         <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>4.33</v>
+        <v>2.23</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="R20" t="n">
-        <v>1.73</v>
+        <v>3.26</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4392,10 +4392,10 @@
         <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.72</v>
+        <v>2.15</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.98</v>
+        <v>1.61</v>
       </c>
       <c r="AG20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>3.32</v>
+        <v>3.98</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.48</v>
+        <v>3.62</v>
       </c>
       <c r="R21" t="n">
-        <v>2.09</v>
+        <v>1.85</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AF21" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -4983,10 +4983,10 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5180,10 +5180,10 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.76</v>
+        <v>2.64</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.13</v>
+        <v>3.15</v>
       </c>
       <c r="R26" t="n">
-        <v>2.57</v>
+        <v>2.66</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5574,10 +5574,10 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.66</v>
+        <v>2.1</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="AG26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="R27" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5771,10 +5771,10 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Jamshedpur</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>5.84</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.41</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Jamshedpur</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>5.84</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="R46" t="n">
-        <v>3.63</v>
+        <v>4.91</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>3.02</v>
+        <v>2.34</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="R67" t="n">
-        <v>2.15</v>
+        <v>2.93</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13651,10 +13651,10 @@
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF67" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG67" t="n">
         <v>0</v>
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13799,17 +13799,17 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -13996,17 +13996,17 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P69" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>2.34</v>
+        <v>3.76</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="R70" t="n">
-        <v>2.93</v>
+        <v>1.98</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14242,10 +14242,10 @@
         <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF70" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>2.58</v>
+        <v>3.02</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.12</v>
+        <v>3.6</v>
       </c>
       <c r="R71" t="n">
-        <v>2.73</v>
+        <v>2.15</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>4.51</v>
+        <v>2.31</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.58</v>
+        <v>3.16</v>
       </c>
       <c r="R77" t="n">
-        <v>1.77</v>
+        <v>2.86</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>1.74</v>
+        <v>2.37</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.62</v>
+        <v>3.2</v>
       </c>
       <c r="R78" t="n">
-        <v>4.02</v>
+        <v>2.7</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15818,10 +15818,10 @@
         <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF78" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1.74</v>
+        <v>4.51</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.52</v>
+        <v>3.58</v>
       </c>
       <c r="R79" t="n">
-        <v>4.17</v>
+        <v>1.77</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16015,10 +16015,10 @@
         <v>0</v>
       </c>
       <c r="AE79" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF79" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG79" t="n">
         <v>0</v>
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.62</v>
+        <v>3.52</v>
       </c>
       <c r="R80" t="n">
-        <v>4.4</v>
+        <v>4.17</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16212,10 +16212,10 @@
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="AF80" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AG80" t="n">
         <v>0</v>
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>2.87</v>
+        <v>2</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.4</v>
+        <v>3.54</v>
       </c>
       <c r="R81" t="n">
-        <v>2.3</v>
+        <v>3.52</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>2.16</v>
+        <v>1.68</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.5</v>
+        <v>3.62</v>
       </c>
       <c r="R83" t="n">
-        <v>3.14</v>
+        <v>4.4</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16803,10 +16803,10 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>2.03</v>
+        <v>1.82</v>
       </c>
       <c r="AF83" t="n">
-        <v>1.78</v>
+        <v>1.94</v>
       </c>
       <c r="AG83" t="n">
         <v>0</v>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>2.31</v>
+        <v>2.16</v>
       </c>
       <c r="Q84" t="n">
-        <v>3.16</v>
+        <v>3.5</v>
       </c>
       <c r="R84" t="n">
-        <v>2.86</v>
+        <v>3.14</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17000,10 +17000,10 @@
         <v>0</v>
       </c>
       <c r="AE84" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF84" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG84" t="n">
         <v>0</v>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q85" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R85" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>2</v>
+        <v>3.74</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.54</v>
+        <v>3.45</v>
       </c>
       <c r="R87" t="n">
-        <v>3.52</v>
+        <v>1.88</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>3.74</v>
+        <v>1.42</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.45</v>
+        <v>4.3</v>
       </c>
       <c r="R88" t="n">
-        <v>1.88</v>
+        <v>6.55</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1.42</v>
+        <v>2.1</v>
       </c>
       <c r="Q90" t="n">
-        <v>4.3</v>
+        <v>3.15</v>
       </c>
       <c r="R90" t="n">
-        <v>6.55</v>
+        <v>3.35</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>2.32</v>
+        <v>1.74</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.1</v>
+        <v>3.62</v>
       </c>
       <c r="R91" t="n">
-        <v>2.99</v>
+        <v>4.02</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18379,10 +18379,10 @@
         <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF91" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG91" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>2.37</v>
+        <v>2.87</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="R92" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Q93" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>4.58</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -18970,10 +18970,10 @@
         <v>0</v>
       </c>
       <c r="AE94" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF94" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG94" t="n">
         <v>0</v>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q95" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1.26</v>
+        <v>1.92</v>
       </c>
       <c r="Q96" t="n">
-        <v>6.15</v>
+        <v>3.3</v>
       </c>
       <c r="R96" t="n">
-        <v>8.949999999999999</v>
+        <v>4.14</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q98" t="n">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19758,10 +19758,10 @@
         <v>0</v>
       </c>
       <c r="AE98" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF98" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG98" t="n">
         <v>0</v>
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,22 +22817,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,22 +23802,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,22 +23999,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G129" t="n">

--- a/jogos_2026-05-01.xlsx
+++ b/jogos_2026-05-01.xlsx
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.66</v>
+        <v>2.64</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.94</v>
+        <v>3.15</v>
       </c>
       <c r="R16" t="n">
-        <v>4.74</v>
+        <v>2.66</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3604,10 +3604,10 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.66</v>
+        <v>2.1</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.76</v>
+        <v>1.66</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.13</v>
+        <v>3.94</v>
       </c>
       <c r="R18" t="n">
-        <v>2.57</v>
+        <v>4.74</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.23</v>
+        <v>3.98</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.2</v>
+        <v>3.62</v>
       </c>
       <c r="R20" t="n">
-        <v>3.26</v>
+        <v>1.85</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4392,10 +4392,10 @@
         <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.61</v>
+        <v>1.9</v>
       </c>
       <c r="AG20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>3.98</v>
+        <v>2.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.62</v>
+        <v>3.25</v>
       </c>
       <c r="R21" t="n">
-        <v>1.85</v>
+        <v>3.25</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.59</v>
+        <v>2.23</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.98</v>
+        <v>3.2</v>
       </c>
       <c r="R22" t="n">
-        <v>5.35</v>
+        <v>3.26</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.78</v>
+        <v>2.15</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.9</v>
+        <v>1.61</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>4.33</v>
+        <v>2.76</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.8</v>
+        <v>3.13</v>
       </c>
       <c r="R24" t="n">
-        <v>1.73</v>
+        <v>2.57</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5180,10 +5180,10 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.64</v>
+        <v>4.33</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.15</v>
+        <v>3.8</v>
       </c>
       <c r="R26" t="n">
-        <v>2.66</v>
+        <v>1.73</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5574,10 +5574,10 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.1</v>
+        <v>1.72</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.65</v>
+        <v>1.98</v>
       </c>
       <c r="AG26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.2</v>
+        <v>1.59</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.25</v>
+        <v>3.98</v>
       </c>
       <c r="R27" t="n">
-        <v>3.25</v>
+        <v>5.35</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5771,10 +5771,10 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.1</v>
+        <v>1.78</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Jamshedpur</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Jamshedpur</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>5.84</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>5.84</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>4.41</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13602,17 +13602,17 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P67" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13651,10 +13651,10 @@
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF67" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>2.58</v>
+        <v>3.02</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.12</v>
+        <v>3.6</v>
       </c>
       <c r="R68" t="n">
-        <v>2.73</v>
+        <v>2.15</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -13996,17 +13996,17 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>3.76</v>
+        <v>2.58</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="R70" t="n">
-        <v>1.98</v>
+        <v>2.73</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>3.02</v>
+        <v>2.34</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="R71" t="n">
-        <v>2.15</v>
+        <v>2.93</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14439,10 +14439,10 @@
         <v>0</v>
       </c>
       <c r="AE71" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF71" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG71" t="n">
         <v>0</v>
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF72" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2.31</v>
+        <v>2.1</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="R77" t="n">
-        <v>2.86</v>
+        <v>3.35</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>2.37</v>
+        <v>3.74</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="R78" t="n">
-        <v>2.7</v>
+        <v>1.88</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>4.51</v>
+        <v>2.32</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.58</v>
+        <v>3.1</v>
       </c>
       <c r="R79" t="n">
-        <v>1.77</v>
+        <v>2.99</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1.74</v>
+        <v>2.37</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.52</v>
+        <v>3.2</v>
       </c>
       <c r="R80" t="n">
-        <v>4.17</v>
+        <v>2.7</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16212,10 +16212,10 @@
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF80" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG80" t="n">
         <v>0</v>
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>2</v>
+        <v>1.42</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.54</v>
+        <v>4.3</v>
       </c>
       <c r="R81" t="n">
-        <v>3.52</v>
+        <v>6.55</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>1.92</v>
+        <v>1.45</v>
       </c>
       <c r="Q82" t="n">
-        <v>3.91</v>
+        <v>4.05</v>
       </c>
       <c r="R82" t="n">
-        <v>3.71</v>
+        <v>6.12</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16606,10 +16606,10 @@
         <v>0</v>
       </c>
       <c r="AE82" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF82" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG82" t="n">
         <v>0</v>
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16803,10 +16803,10 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF83" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG83" t="n">
         <v>0</v>
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>2.16</v>
+        <v>4.51</v>
       </c>
       <c r="Q84" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="R84" t="n">
-        <v>3.14</v>
+        <v>1.77</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17000,10 +17000,10 @@
         <v>0</v>
       </c>
       <c r="AE84" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF84" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG84" t="n">
         <v>0</v>
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>2.32</v>
+        <v>1.74</v>
       </c>
       <c r="Q85" t="n">
-        <v>3.1</v>
+        <v>3.62</v>
       </c>
       <c r="R85" t="n">
-        <v>2.99</v>
+        <v>4.02</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17197,10 +17197,10 @@
         <v>0</v>
       </c>
       <c r="AE85" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF85" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG85" t="n">
         <v>0</v>
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>1.45</v>
+        <v>2.16</v>
       </c>
       <c r="Q86" t="n">
-        <v>4.05</v>
+        <v>3.5</v>
       </c>
       <c r="R86" t="n">
-        <v>6.12</v>
+        <v>3.14</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17394,10 +17394,10 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>1.82</v>
+        <v>2.03</v>
       </c>
       <c r="AF86" t="n">
-        <v>1.94</v>
+        <v>1.78</v>
       </c>
       <c r="AG86" t="n">
         <v>0</v>
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>3.74</v>
+        <v>2</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.45</v>
+        <v>3.54</v>
       </c>
       <c r="R87" t="n">
-        <v>1.88</v>
+        <v>3.52</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>1.42</v>
+        <v>1.68</v>
       </c>
       <c r="Q88" t="n">
-        <v>4.3</v>
+        <v>3.62</v>
       </c>
       <c r="R88" t="n">
-        <v>6.55</v>
+        <v>4.4</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17788,10 +17788,10 @@
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF88" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG88" t="n">
         <v>0</v>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Q89" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R89" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>2.1</v>
+        <v>1.74</v>
       </c>
       <c r="Q90" t="n">
-        <v>3.15</v>
+        <v>3.52</v>
       </c>
       <c r="R90" t="n">
-        <v>3.35</v>
+        <v>4.17</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18182,10 +18182,10 @@
         <v>0</v>
       </c>
       <c r="AE90" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF90" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG90" t="n">
         <v>0</v>
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1.74</v>
+        <v>2.31</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.62</v>
+        <v>3.16</v>
       </c>
       <c r="R91" t="n">
-        <v>4.02</v>
+        <v>2.86</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18379,10 +18379,10 @@
         <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF91" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG91" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>2.87</v>
+        <v>1.92</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.4</v>
+        <v>3.91</v>
       </c>
       <c r="R92" t="n">
-        <v>2.3</v>
+        <v>3.71</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>1.26</v>
+        <v>1.92</v>
       </c>
       <c r="Q93" t="n">
-        <v>6.15</v>
+        <v>3.3</v>
       </c>
       <c r="R93" t="n">
-        <v>8.949999999999999</v>
+        <v>4.14</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1.92</v>
+        <v>1.26</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.3</v>
+        <v>6.15</v>
       </c>
       <c r="R96" t="n">
-        <v>4.14</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q97" t="n">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="R97" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19561,10 +19561,10 @@
         <v>0</v>
       </c>
       <c r="AE97" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF97" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG97" t="n">
         <v>0</v>
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Q98" t="n">
-        <v>4.58</v>
+        <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19758,10 +19758,10 @@
         <v>0</v>
       </c>
       <c r="AE98" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF98" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG98" t="n">
         <v>0</v>
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,22 +23802,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G129" t="n">

--- a/jogos_2026-05-01.xlsx
+++ b/jogos_2026-05-01.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1240,10 +1240,10 @@
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1437,10 +1437,10 @@
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.64</v>
+        <v>2.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="R16" t="n">
-        <v>2.66</v>
+        <v>3.25</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.29</v>
+        <v>4.33</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.14</v>
+        <v>3.8</v>
       </c>
       <c r="R17" t="n">
-        <v>3.21</v>
+        <v>1.73</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3801,10 +3801,10 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.94</v>
+        <v>3.98</v>
       </c>
       <c r="R18" t="n">
-        <v>4.74</v>
+        <v>5.35</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -3998,10 +3998,10 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.66</v>
+        <v>1.78</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>3.32</v>
+        <v>2.64</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.48</v>
+        <v>3.15</v>
       </c>
       <c r="R19" t="n">
-        <v>2.09</v>
+        <v>2.66</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4195,10 +4195,10 @@
         <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.71</v>
+        <v>2.1</v>
       </c>
       <c r="AF19" t="n">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>3.98</v>
+        <v>2.76</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.62</v>
+        <v>3.13</v>
       </c>
       <c r="R20" t="n">
-        <v>1.85</v>
+        <v>2.57</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4392,10 +4392,10 @@
         <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AG20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.2</v>
+        <v>1.66</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.25</v>
+        <v>3.94</v>
       </c>
       <c r="R21" t="n">
-        <v>3.25</v>
+        <v>4.74</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.1</v>
+        <v>1.66</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -4983,10 +4983,10 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.76</v>
+        <v>2.23</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.13</v>
+        <v>3.2</v>
       </c>
       <c r="R24" t="n">
-        <v>2.57</v>
+        <v>3.26</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5180,10 +5180,10 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.66</v>
+        <v>2.15</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.05</v>
+        <v>1.61</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5574,10 +5574,10 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.59</v>
+        <v>3.98</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.98</v>
+        <v>3.62</v>
       </c>
       <c r="R27" t="n">
-        <v>5.35</v>
+        <v>1.85</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AF27" t="n">
         <v>1.9</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Jamshedpur</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>5.84</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.41</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>5.84</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Jamshedpur</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.94</v>
+        <v>2.73</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.72</v>
+        <v>3.16</v>
       </c>
       <c r="R41" t="n">
-        <v>3.46</v>
+        <v>2.34</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="R45" t="n">
-        <v>3.63</v>
+        <v>4.91</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="R46" t="n">
-        <v>4.91</v>
+        <v>3.63</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1.68</v>
+        <v>2.09</v>
       </c>
       <c r="Q58" t="n">
-        <v>4.11</v>
+        <v>3.15</v>
       </c>
       <c r="R58" t="n">
-        <v>4.45</v>
+        <v>3.31</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13602,17 +13602,17 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>3.02</v>
+        <v>3.76</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="R68" t="n">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>3.76</v>
+        <v>2.34</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="R69" t="n">
-        <v>1.98</v>
+        <v>2.93</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,10 +14045,10 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF69" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14390,17 +14390,17 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P71" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14439,10 +14439,10 @@
         <v>0</v>
       </c>
       <c r="AE71" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF71" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG71" t="n">
         <v>0</v>
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF72" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14833,10 +14833,10 @@
         <v>0</v>
       </c>
       <c r="AE73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF73" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG73" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>2.1</v>
+        <v>3.62</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="R75" t="n">
-        <v>3.41</v>
+        <v>1.86</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>3.62</v>
+        <v>2.1</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="R76" t="n">
-        <v>1.86</v>
+        <v>3.41</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2.1</v>
+        <v>4.51</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.15</v>
+        <v>3.58</v>
       </c>
       <c r="R77" t="n">
-        <v>3.35</v>
+        <v>1.77</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>3.74</v>
+        <v>1.92</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.45</v>
+        <v>3.91</v>
       </c>
       <c r="R78" t="n">
-        <v>1.88</v>
+        <v>3.71</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R79" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>2.37</v>
+        <v>1.45</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.2</v>
+        <v>4.05</v>
       </c>
       <c r="R80" t="n">
-        <v>2.7</v>
+        <v>6.12</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16212,10 +16212,10 @@
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF80" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1.42</v>
+        <v>2.87</v>
       </c>
       <c r="Q81" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="R81" t="n">
-        <v>6.55</v>
+        <v>2.3</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>1.45</v>
+        <v>2.31</v>
       </c>
       <c r="Q82" t="n">
-        <v>4.05</v>
+        <v>3.16</v>
       </c>
       <c r="R82" t="n">
-        <v>6.12</v>
+        <v>2.86</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16606,10 +16606,10 @@
         <v>0</v>
       </c>
       <c r="AE82" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF82" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG82" t="n">
         <v>0</v>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q83" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>4.51</v>
+        <v>1.74</v>
       </c>
       <c r="Q84" t="n">
-        <v>3.58</v>
+        <v>3.62</v>
       </c>
       <c r="R84" t="n">
-        <v>1.77</v>
+        <v>4.02</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17000,10 +17000,10 @@
         <v>0</v>
       </c>
       <c r="AE84" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF84" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG84" t="n">
         <v>0</v>
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17155,10 +17155,10 @@
         <v>1.74</v>
       </c>
       <c r="Q85" t="n">
-        <v>3.62</v>
+        <v>3.52</v>
       </c>
       <c r="R85" t="n">
-        <v>4.02</v>
+        <v>4.17</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17197,10 +17197,10 @@
         <v>0</v>
       </c>
       <c r="AE85" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF85" t="n">
         <v>1.85</v>
-      </c>
-      <c r="AF85" t="n">
-        <v>1.9</v>
       </c>
       <c r="AG85" t="n">
         <v>0</v>
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>2.16</v>
+        <v>1.42</v>
       </c>
       <c r="Q86" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="R86" t="n">
-        <v>3.14</v>
+        <v>6.55</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17394,10 +17394,10 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF86" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG86" t="n">
         <v>0</v>
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.54</v>
+        <v>3.15</v>
       </c>
       <c r="R87" t="n">
-        <v>3.52</v>
+        <v>3.35</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>1.68</v>
+        <v>3.74</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.62</v>
+        <v>3.45</v>
       </c>
       <c r="R88" t="n">
-        <v>4.4</v>
+        <v>1.88</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17788,10 +17788,10 @@
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF88" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG88" t="n">
         <v>0</v>
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>2.87</v>
+        <v>1.68</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.4</v>
+        <v>3.62</v>
       </c>
       <c r="R89" t="n">
-        <v>2.3</v>
+        <v>4.4</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -17985,10 +17985,10 @@
         <v>0</v>
       </c>
       <c r="AE89" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF89" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG89" t="n">
         <v>0</v>
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1.74</v>
+        <v>2.16</v>
       </c>
       <c r="Q90" t="n">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="R90" t="n">
-        <v>4.17</v>
+        <v>3.14</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18182,10 +18182,10 @@
         <v>0</v>
       </c>
       <c r="AE90" t="n">
-        <v>1.91</v>
+        <v>2.03</v>
       </c>
       <c r="AF90" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AG90" t="n">
         <v>0</v>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>2.31</v>
+        <v>2</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.16</v>
+        <v>3.54</v>
       </c>
       <c r="R91" t="n">
-        <v>2.86</v>
+        <v>3.52</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>1.92</v>
+        <v>2.32</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.91</v>
+        <v>3.1</v>
       </c>
       <c r="R92" t="n">
-        <v>3.71</v>
+        <v>2.99</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q98" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="G129" t="n">

--- a/jogos_2026-05-01.xlsx
+++ b/jogos_2026-05-01.xlsx
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="R10" t="n">
-        <v>2.43</v>
+        <v>3</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Kuching FA</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kuching FA</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.2</v>
+        <v>3.32</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.25</v>
+        <v>3.48</v>
       </c>
       <c r="R16" t="n">
-        <v>3.25</v>
+        <v>2.09</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3604,10 +3604,10 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.1</v>
+        <v>1.71</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>4.33</v>
+        <v>2.76</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.8</v>
+        <v>3.13</v>
       </c>
       <c r="R17" t="n">
-        <v>1.73</v>
+        <v>2.57</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3801,10 +3801,10 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.64</v>
+        <v>3.98</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.15</v>
+        <v>3.62</v>
       </c>
       <c r="R19" t="n">
-        <v>2.66</v>
+        <v>1.85</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4195,10 +4195,10 @@
         <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AG19" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4392,10 +4392,10 @@
         <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.66</v>
+        <v>2.29</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.94</v>
+        <v>3.14</v>
       </c>
       <c r="R21" t="n">
-        <v>4.74</v>
+        <v>3.21</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.66</v>
+        <v>1.83</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.29</v>
+        <v>1.66</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.14</v>
+        <v>3.94</v>
       </c>
       <c r="R23" t="n">
-        <v>3.21</v>
+        <v>4.74</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -4983,10 +4983,10 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.83</v>
+        <v>1.66</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AG23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.23</v>
+        <v>2.64</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="R24" t="n">
-        <v>3.26</v>
+        <v>2.66</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5180,10 +5180,10 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3.32</v>
+        <v>2.2</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.48</v>
+        <v>3.25</v>
       </c>
       <c r="R25" t="n">
-        <v>2.09</v>
+        <v>3.25</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.71</v>
+        <v>2.1</v>
       </c>
       <c r="AF25" t="n">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5574,10 +5574,10 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>3.98</v>
+        <v>4.33</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.62</v>
+        <v>3.8</v>
       </c>
       <c r="R27" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5771,10 +5771,10 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Jamshedpur</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Jamshedpur</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.73</v>
+        <v>1.94</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.16</v>
+        <v>3.72</v>
       </c>
       <c r="R41" t="n">
-        <v>2.34</v>
+        <v>3.46</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9120,10 +9120,10 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="R45" t="n">
-        <v>4.91</v>
+        <v>3.63</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="R46" t="n">
-        <v>3.63</v>
+        <v>4.91</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF60" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13602,17 +13602,17 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P67" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>3.76</v>
+        <v>3.02</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="R68" t="n">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>2.34</v>
+        <v>2.58</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.25</v>
+        <v>3.12</v>
       </c>
       <c r="R69" t="n">
-        <v>2.93</v>
+        <v>2.73</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,10 +14045,10 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF69" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>2.58</v>
+        <v>3.76</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="R70" t="n">
-        <v>2.73</v>
+        <v>1.98</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14390,17 +14390,17 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14439,10 +14439,10 @@
         <v>0</v>
       </c>
       <c r="AE71" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF71" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG71" t="n">
         <v>0</v>
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF72" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14833,10 +14833,10 @@
         <v>0</v>
       </c>
       <c r="AE73" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF73" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG73" t="n">
         <v>0</v>
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>4.51</v>
+        <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>1.92</v>
+        <v>1.42</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.91</v>
+        <v>4.3</v>
       </c>
       <c r="R78" t="n">
-        <v>3.71</v>
+        <v>6.55</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R79" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1.45</v>
+        <v>3.74</v>
       </c>
       <c r="Q80" t="n">
-        <v>4.05</v>
+        <v>3.45</v>
       </c>
       <c r="R80" t="n">
-        <v>6.12</v>
+        <v>1.88</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16212,10 +16212,10 @@
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF80" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>2.87</v>
+        <v>2.1</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="R81" t="n">
-        <v>2.3</v>
+        <v>3.35</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>2.31</v>
+        <v>1.92</v>
       </c>
       <c r="Q82" t="n">
-        <v>3.16</v>
+        <v>3.91</v>
       </c>
       <c r="R82" t="n">
-        <v>2.86</v>
+        <v>3.71</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>2.37</v>
+        <v>2.16</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="R83" t="n">
-        <v>2.7</v>
+        <v>3.14</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16803,10 +16803,10 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF83" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG83" t="n">
         <v>0</v>
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>1.74</v>
+        <v>2.31</v>
       </c>
       <c r="Q84" t="n">
-        <v>3.62</v>
+        <v>3.16</v>
       </c>
       <c r="R84" t="n">
-        <v>4.02</v>
+        <v>2.86</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17000,10 +17000,10 @@
         <v>0</v>
       </c>
       <c r="AE84" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF84" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG84" t="n">
         <v>0</v>
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="Q85" t="n">
-        <v>3.52</v>
+        <v>3.62</v>
       </c>
       <c r="R85" t="n">
-        <v>4.17</v>
+        <v>4.4</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17197,10 +17197,10 @@
         <v>0</v>
       </c>
       <c r="AE85" t="n">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="AF85" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AG85" t="n">
         <v>0</v>
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>1.42</v>
+        <v>2.37</v>
       </c>
       <c r="Q86" t="n">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
       <c r="R86" t="n">
-        <v>6.55</v>
+        <v>2.7</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>2.1</v>
+        <v>2.32</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="R87" t="n">
-        <v>3.35</v>
+        <v>2.99</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>3.74</v>
+        <v>1.74</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.45</v>
+        <v>3.62</v>
       </c>
       <c r="R88" t="n">
-        <v>1.88</v>
+        <v>4.02</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17788,10 +17788,10 @@
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF88" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG88" t="n">
         <v>0</v>
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>1.68</v>
+        <v>2.87</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.62</v>
+        <v>3.4</v>
       </c>
       <c r="R89" t="n">
-        <v>4.4</v>
+        <v>2.3</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -17985,10 +17985,10 @@
         <v>0</v>
       </c>
       <c r="AE89" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF89" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG89" t="n">
         <v>0</v>
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>2.16</v>
+        <v>4.51</v>
       </c>
       <c r="Q90" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="R90" t="n">
-        <v>3.14</v>
+        <v>1.77</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18182,10 +18182,10 @@
         <v>0</v>
       </c>
       <c r="AE90" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF90" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG90" t="n">
         <v>0</v>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.54</v>
+        <v>3.52</v>
       </c>
       <c r="R91" t="n">
-        <v>3.52</v>
+        <v>4.17</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18379,10 +18379,10 @@
         <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF91" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG91" t="n">
         <v>0</v>
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>2.32</v>
+        <v>1.45</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.1</v>
+        <v>4.05</v>
       </c>
       <c r="R92" t="n">
-        <v>2.99</v>
+        <v>6.12</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18576,10 +18576,10 @@
         <v>0</v>
       </c>
       <c r="AE92" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF92" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG92" t="n">
         <v>0</v>
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q93" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18773,10 +18773,10 @@
         <v>0</v>
       </c>
       <c r="AE93" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF93" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG93" t="n">
         <v>0</v>
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -18970,10 +18970,10 @@
         <v>0</v>
       </c>
       <c r="AE94" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF94" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG94" t="n">
         <v>0</v>
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>1.5</v>
+        <v>1.92</v>
       </c>
       <c r="Q97" t="n">
-        <v>4.58</v>
+        <v>3.3</v>
       </c>
       <c r="R97" t="n">
-        <v>7.8</v>
+        <v>4.14</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19561,10 +19561,10 @@
         <v>0</v>
       </c>
       <c r="AE97" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF97" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG97" t="n">
         <v>0</v>
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q98" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q105" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R105" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,22 +24196,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G128" t="n">

--- a/jogos_2026-05-01.xlsx
+++ b/jogos_2026-05-01.xlsx
@@ -950,22 +950,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1240,10 +1240,10 @@
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1437,10 +1437,10 @@
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2028,10 +2028,10 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="R10" t="n">
-        <v>3</v>
+        <v>2.43</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kuching FA</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Kuching FA</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>3.32</v>
+        <v>2.29</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.48</v>
+        <v>3.14</v>
       </c>
       <c r="R16" t="n">
-        <v>2.09</v>
+        <v>3.21</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3604,10 +3604,10 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="AF16" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.76</v>
+        <v>1.66</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.13</v>
+        <v>3.94</v>
       </c>
       <c r="R17" t="n">
-        <v>2.57</v>
+        <v>4.74</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.59</v>
+        <v>2.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.98</v>
+        <v>3.25</v>
       </c>
       <c r="R18" t="n">
-        <v>5.35</v>
+        <v>3.25</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -3998,10 +3998,10 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.78</v>
+        <v>2.1</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>3.98</v>
+        <v>2.64</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.62</v>
+        <v>3.15</v>
       </c>
       <c r="R19" t="n">
-        <v>1.85</v>
+        <v>2.66</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4195,10 +4195,10 @@
         <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AG19" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4392,10 +4392,10 @@
         <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.66</v>
+        <v>2.23</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.94</v>
+        <v>3.2</v>
       </c>
       <c r="R23" t="n">
-        <v>4.74</v>
+        <v>3.26</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -4983,10 +4983,10 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.66</v>
+        <v>2.15</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.05</v>
+        <v>1.61</v>
       </c>
       <c r="AG23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.64</v>
+        <v>1.59</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.15</v>
+        <v>3.98</v>
       </c>
       <c r="R24" t="n">
-        <v>2.66</v>
+        <v>5.35</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5180,10 +5180,10 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.1</v>
+        <v>1.78</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.2</v>
+        <v>3.98</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.25</v>
+        <v>3.62</v>
       </c>
       <c r="R25" t="n">
-        <v>3.25</v>
+        <v>1.85</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.23</v>
+        <v>4.33</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="R26" t="n">
-        <v>3.26</v>
+        <v>1.73</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5574,10 +5574,10 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.15</v>
+        <v>1.72</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.61</v>
+        <v>1.98</v>
       </c>
       <c r="AG26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5771,10 +5771,10 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>5.84</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>5.84</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>4.41</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Jamshedpur</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Jamshedpur</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.94</v>
+        <v>2.73</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.72</v>
+        <v>3.16</v>
       </c>
       <c r="R41" t="n">
-        <v>3.46</v>
+        <v>2.34</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="R45" t="n">
-        <v>3.63</v>
+        <v>4.91</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="R46" t="n">
-        <v>4.91</v>
+        <v>3.63</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>2.31</v>
+        <v>1.76</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.9</v>
+        <v>3.91</v>
       </c>
       <c r="R59" t="n">
-        <v>3.08</v>
+        <v>4.58</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12075,10 +12075,10 @@
         <v>0</v>
       </c>
       <c r="AE59" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF59" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG59" t="n">
         <v>0</v>
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1.76</v>
+        <v>2.38</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.91</v>
+        <v>3.2</v>
       </c>
       <c r="R60" t="n">
-        <v>4.58</v>
+        <v>2.75</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF60" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13602,17 +13602,17 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>2.58</v>
+        <v>2.34</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
       <c r="R69" t="n">
-        <v>2.73</v>
+        <v>2.93</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,10 +14045,10 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF69" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>3.76</v>
+        <v>2.58</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="R70" t="n">
-        <v>1.98</v>
+        <v>2.73</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14390,17 +14390,17 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P71" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14439,10 +14439,10 @@
         <v>0</v>
       </c>
       <c r="AE71" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF71" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG71" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>3.62</v>
+        <v>2.1</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="R75" t="n">
-        <v>1.86</v>
+        <v>3.41</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>2.1</v>
+        <v>3.62</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="R76" t="n">
-        <v>3.41</v>
+        <v>1.86</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>1.42</v>
+        <v>3.74</v>
       </c>
       <c r="Q78" t="n">
-        <v>4.3</v>
+        <v>3.45</v>
       </c>
       <c r="R78" t="n">
-        <v>6.55</v>
+        <v>1.88</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>3.74</v>
+        <v>1.74</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.45</v>
+        <v>3.52</v>
       </c>
       <c r="R80" t="n">
-        <v>1.88</v>
+        <v>4.17</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16212,10 +16212,10 @@
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF80" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG80" t="n">
         <v>0</v>
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>1.92</v>
+        <v>2.16</v>
       </c>
       <c r="Q82" t="n">
-        <v>3.91</v>
+        <v>3.5</v>
       </c>
       <c r="R82" t="n">
-        <v>3.71</v>
+        <v>3.14</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16606,10 +16606,10 @@
         <v>0</v>
       </c>
       <c r="AE82" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF82" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG82" t="n">
         <v>0</v>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>2.16</v>
+        <v>1.68</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.5</v>
+        <v>3.62</v>
       </c>
       <c r="R83" t="n">
-        <v>3.14</v>
+        <v>4.4</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16803,10 +16803,10 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>2.03</v>
+        <v>1.82</v>
       </c>
       <c r="AF83" t="n">
-        <v>1.78</v>
+        <v>1.94</v>
       </c>
       <c r="AG83" t="n">
         <v>0</v>
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>2.31</v>
+        <v>2.37</v>
       </c>
       <c r="Q84" t="n">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="R84" t="n">
-        <v>2.86</v>
+        <v>2.7</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>1.68</v>
+        <v>4.51</v>
       </c>
       <c r="Q85" t="n">
-        <v>3.62</v>
+        <v>3.58</v>
       </c>
       <c r="R85" t="n">
-        <v>4.4</v>
+        <v>1.77</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17197,10 +17197,10 @@
         <v>0</v>
       </c>
       <c r="AE85" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF85" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG85" t="n">
         <v>0</v>
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>2.37</v>
+        <v>1.45</v>
       </c>
       <c r="Q86" t="n">
-        <v>3.2</v>
+        <v>4.05</v>
       </c>
       <c r="R86" t="n">
-        <v>2.7</v>
+        <v>6.12</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17394,10 +17394,10 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF86" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG86" t="n">
         <v>0</v>
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>1.74</v>
+        <v>1.92</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.62</v>
+        <v>3.91</v>
       </c>
       <c r="R88" t="n">
-        <v>4.02</v>
+        <v>3.71</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17788,10 +17788,10 @@
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF88" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG88" t="n">
         <v>0</v>
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>2.87</v>
+        <v>1.74</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.4</v>
+        <v>3.62</v>
       </c>
       <c r="R89" t="n">
-        <v>2.3</v>
+        <v>4.02</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -17985,10 +17985,10 @@
         <v>0</v>
       </c>
       <c r="AE89" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF89" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG89" t="n">
         <v>0</v>
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>4.51</v>
+        <v>1.42</v>
       </c>
       <c r="Q90" t="n">
-        <v>3.58</v>
+        <v>4.3</v>
       </c>
       <c r="R90" t="n">
-        <v>1.77</v>
+        <v>6.55</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18379,10 +18379,10 @@
         <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF91" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG91" t="n">
         <v>0</v>
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>1.45</v>
+        <v>2.87</v>
       </c>
       <c r="Q92" t="n">
-        <v>4.05</v>
+        <v>3.4</v>
       </c>
       <c r="R92" t="n">
-        <v>6.12</v>
+        <v>2.3</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18576,10 +18576,10 @@
         <v>0</v>
       </c>
       <c r="AE92" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF92" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG92" t="n">
         <v>0</v>
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>2.1</v>
+        <v>1.26</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.45</v>
+        <v>6.15</v>
       </c>
       <c r="R93" t="n">
-        <v>3.63</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18773,10 +18773,10 @@
         <v>0</v>
       </c>
       <c r="AE93" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF93" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG93" t="n">
         <v>0</v>
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q95" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1.26</v>
+        <v>2.1</v>
       </c>
       <c r="Q96" t="n">
-        <v>6.15</v>
+        <v>3.45</v>
       </c>
       <c r="R96" t="n">
-        <v>8.949999999999999</v>
+        <v>3.63</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,10 +19364,10 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF96" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q97" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q105" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R105" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,22 +24196,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,22 +25378,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25426,13 +25426,13 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q127" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R127" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G129" t="n">

--- a/jogos_2026-05-01.xlsx
+++ b/jogos_2026-05-01.xlsx
@@ -950,22 +950,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.93</v>
+        <v>4.54</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.98</v>
+        <v>3.7</v>
       </c>
       <c r="R7" t="n">
-        <v>2.71</v>
+        <v>1.66</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2028,10 +2028,10 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="R11" t="n">
-        <v>3</v>
+        <v>2.43</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.29</v>
+        <v>3.98</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.14</v>
+        <v>3.62</v>
       </c>
       <c r="R16" t="n">
-        <v>3.21</v>
+        <v>1.85</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3604,10 +3604,10 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.94</v>
+        <v>3.98</v>
       </c>
       <c r="R17" t="n">
-        <v>4.74</v>
+        <v>5.35</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3801,10 +3801,10 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.66</v>
+        <v>1.78</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.2</v>
+        <v>2.29</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.25</v>
+        <v>3.14</v>
       </c>
       <c r="R18" t="n">
-        <v>3.25</v>
+        <v>3.21</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -3998,10 +3998,10 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.64</v>
+        <v>1.66</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.15</v>
+        <v>3.94</v>
       </c>
       <c r="R19" t="n">
-        <v>2.66</v>
+        <v>4.74</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4195,10 +4195,10 @@
         <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.1</v>
+        <v>1.66</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="AG19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4392,10 +4392,10 @@
         <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.76</v>
+        <v>4.33</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.13</v>
+        <v>3.8</v>
       </c>
       <c r="R22" t="n">
-        <v>2.57</v>
+        <v>1.73</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.23</v>
+        <v>2.76</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.2</v>
+        <v>3.13</v>
       </c>
       <c r="R23" t="n">
-        <v>3.26</v>
+        <v>2.57</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -4983,10 +4983,10 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.15</v>
+        <v>1.66</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.61</v>
+        <v>2.05</v>
       </c>
       <c r="AG23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.59</v>
+        <v>3.32</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.98</v>
+        <v>3.48</v>
       </c>
       <c r="R24" t="n">
-        <v>5.35</v>
+        <v>2.09</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5180,10 +5180,10 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3.98</v>
+        <v>2.65</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.62</v>
+        <v>3.4</v>
       </c>
       <c r="R25" t="n">
-        <v>1.85</v>
+        <v>2.32</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>4.33</v>
+        <v>2.23</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="R26" t="n">
-        <v>1.73</v>
+        <v>3.26</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5574,10 +5574,10 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.72</v>
+        <v>2.15</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.98</v>
+        <v>1.61</v>
       </c>
       <c r="AG26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5771,10 +5771,10 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Jamshedpur</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>5.84</v>
+        <v>1.94</v>
       </c>
       <c r="Q34" t="n">
-        <v>4.41</v>
+        <v>3.72</v>
       </c>
       <c r="R34" t="n">
-        <v>1.62</v>
+        <v>3.46</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>6.52</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>4.84</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>5.84</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Jamshedpur</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>3.8</v>
+        <v>2.57</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.45</v>
+        <v>3.19</v>
       </c>
       <c r="R52" t="n">
-        <v>1.85</v>
+        <v>2.68</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1.76</v>
+        <v>2.31</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.91</v>
+        <v>3.9</v>
       </c>
       <c r="R59" t="n">
-        <v>4.58</v>
+        <v>3.08</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12075,10 +12075,10 @@
         <v>0</v>
       </c>
       <c r="AE59" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF59" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG59" t="n">
         <v>0</v>
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.38</v>
+        <v>1.76</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.2</v>
+        <v>3.91</v>
       </c>
       <c r="R60" t="n">
-        <v>2.75</v>
+        <v>4.58</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF60" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="R61" t="n">
-        <v>3.08</v>
+        <v>2.75</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>3.02</v>
+        <v>2.58</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.6</v>
+        <v>3.12</v>
       </c>
       <c r="R68" t="n">
-        <v>2.15</v>
+        <v>2.73</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -13996,17 +13996,17 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P69" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,10 +14045,10 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF69" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>2.58</v>
+        <v>3.02</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.12</v>
+        <v>3.6</v>
       </c>
       <c r="R70" t="n">
-        <v>2.73</v>
+        <v>2.15</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14390,17 +14390,17 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14439,10 +14439,10 @@
         <v>0</v>
       </c>
       <c r="AE71" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF71" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG71" t="n">
         <v>0</v>
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2.31</v>
+        <v>2.1</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="R77" t="n">
-        <v>2.86</v>
+        <v>3.35</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>3.74</v>
+        <v>2.37</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="R78" t="n">
-        <v>1.88</v>
+        <v>2.7</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>2</v>
+        <v>2.32</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.54</v>
+        <v>3.1</v>
       </c>
       <c r="R79" t="n">
-        <v>3.52</v>
+        <v>2.99</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1.74</v>
+        <v>4.51</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.52</v>
+        <v>3.58</v>
       </c>
       <c r="R80" t="n">
-        <v>4.17</v>
+        <v>1.77</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16212,10 +16212,10 @@
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF80" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG80" t="n">
         <v>0</v>
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.15</v>
+        <v>3.54</v>
       </c>
       <c r="R81" t="n">
-        <v>3.35</v>
+        <v>3.52</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16606,10 +16606,10 @@
         <v>0</v>
       </c>
       <c r="AE82" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF82" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG82" t="n">
         <v>0</v>
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>1.68</v>
+        <v>1.92</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.62</v>
+        <v>3.91</v>
       </c>
       <c r="R83" t="n">
-        <v>4.4</v>
+        <v>3.71</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16803,10 +16803,10 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF83" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG83" t="n">
         <v>0</v>
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>2.37</v>
+        <v>2.31</v>
       </c>
       <c r="Q84" t="n">
-        <v>3.2</v>
+        <v>3.16</v>
       </c>
       <c r="R84" t="n">
-        <v>2.7</v>
+        <v>2.86</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>4.51</v>
+        <v>1.68</v>
       </c>
       <c r="Q85" t="n">
-        <v>3.58</v>
+        <v>3.62</v>
       </c>
       <c r="R85" t="n">
-        <v>1.77</v>
+        <v>4.4</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17197,10 +17197,10 @@
         <v>0</v>
       </c>
       <c r="AE85" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF85" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG85" t="n">
         <v>0</v>
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>1.45</v>
+        <v>2.16</v>
       </c>
       <c r="Q86" t="n">
-        <v>4.05</v>
+        <v>3.5</v>
       </c>
       <c r="R86" t="n">
-        <v>6.12</v>
+        <v>3.14</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17394,10 +17394,10 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>1.82</v>
+        <v>2.03</v>
       </c>
       <c r="AF86" t="n">
-        <v>1.94</v>
+        <v>1.78</v>
       </c>
       <c r="AG86" t="n">
         <v>0</v>
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>2.32</v>
+        <v>1.45</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.1</v>
+        <v>4.05</v>
       </c>
       <c r="R87" t="n">
-        <v>2.99</v>
+        <v>6.12</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17591,10 +17591,10 @@
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF87" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG87" t="n">
         <v>0</v>
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>1.92</v>
+        <v>1.74</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.91</v>
+        <v>3.62</v>
       </c>
       <c r="R88" t="n">
-        <v>3.71</v>
+        <v>4.02</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17788,10 +17788,10 @@
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF88" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG88" t="n">
         <v>0</v>
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>1.74</v>
+        <v>1.42</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.62</v>
+        <v>4.3</v>
       </c>
       <c r="R89" t="n">
-        <v>4.02</v>
+        <v>6.55</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -17985,10 +17985,10 @@
         <v>0</v>
       </c>
       <c r="AE89" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF89" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG89" t="n">
         <v>0</v>
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1.42</v>
+        <v>3.74</v>
       </c>
       <c r="Q90" t="n">
-        <v>4.3</v>
+        <v>3.45</v>
       </c>
       <c r="R90" t="n">
-        <v>6.55</v>
+        <v>1.88</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Q91" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>2.87</v>
+        <v>1.74</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.4</v>
+        <v>3.52</v>
       </c>
       <c r="R92" t="n">
-        <v>2.3</v>
+        <v>4.17</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18576,10 +18576,10 @@
         <v>0</v>
       </c>
       <c r="AE92" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF92" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG92" t="n">
         <v>0</v>
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>1.26</v>
+        <v>2.1</v>
       </c>
       <c r="Q93" t="n">
-        <v>6.15</v>
+        <v>3.45</v>
       </c>
       <c r="R93" t="n">
-        <v>8.949999999999999</v>
+        <v>3.63</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18773,10 +18773,10 @@
         <v>0</v>
       </c>
       <c r="AE93" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF93" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG93" t="n">
         <v>0</v>
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>4.58</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -18970,10 +18970,10 @@
         <v>0</v>
       </c>
       <c r="AE94" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF94" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG94" t="n">
         <v>0</v>
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>1.92</v>
+        <v>1.26</v>
       </c>
       <c r="Q95" t="n">
-        <v>3.3</v>
+        <v>6.15</v>
       </c>
       <c r="R95" t="n">
-        <v>4.14</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.45</v>
+        <v>4.58</v>
       </c>
       <c r="R96" t="n">
-        <v>3.63</v>
+        <v>7.8</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,10 +19364,10 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>2.15</v>
+        <v>1.68</v>
       </c>
       <c r="AF96" t="n">
-        <v>1.62</v>
+        <v>2.05</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q98" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Q99" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R99" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -19955,10 +19955,10 @@
         <v>0</v>
       </c>
       <c r="AE99" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF99" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG99" t="n">
         <v>0</v>
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q101" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R101" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20349,10 +20349,10 @@
         <v>0</v>
       </c>
       <c r="AE101" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF101" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG101" t="n">
         <v>0</v>
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25181,22 +25181,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25229,13 +25229,13 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q126" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R126" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S126" t="n">
         <v>0</v>
@@ -25378,22 +25378,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25426,13 +25426,13 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q127" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R127" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,22 +25772,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25820,13 +25820,13 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q129" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R129" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="S129" t="n">
         <v>0</v>

--- a/jogos_2026-05-01.xlsx
+++ b/jogos_2026-05-01.xlsx
@@ -950,22 +950,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1147,22 +1147,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1240,10 +1240,10 @@
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1437,10 +1437,10 @@
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.93</v>
+        <v>4.54</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.98</v>
+        <v>3.7</v>
       </c>
       <c r="R6" t="n">
-        <v>2.71</v>
+        <v>1.66</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>4.54</v>
+        <v>2.93</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.7</v>
+        <v>2.98</v>
       </c>
       <c r="R7" t="n">
-        <v>1.66</v>
+        <v>2.71</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Kuching FA</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kuching FA</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>3.98</v>
+        <v>2.76</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.62</v>
+        <v>3.13</v>
       </c>
       <c r="R16" t="n">
-        <v>1.85</v>
+        <v>2.57</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3604,10 +3604,10 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.59</v>
+        <v>2.65</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.98</v>
+        <v>3.4</v>
       </c>
       <c r="R17" t="n">
-        <v>5.35</v>
+        <v>2.32</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3801,10 +3801,10 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.29</v>
+        <v>2.23</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="R18" t="n">
-        <v>3.21</v>
+        <v>3.26</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -3998,10 +3998,10 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="AG18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>4.74</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4195,10 +4195,10 @@
         <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4392,10 +4392,10 @@
         <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.64</v>
+        <v>2.29</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="R21" t="n">
-        <v>2.66</v>
+        <v>3.21</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>4.33</v>
+        <v>2.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="R22" t="n">
-        <v>1.73</v>
+        <v>3.25</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.72</v>
+        <v>2.1</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.98</v>
+        <v>1.65</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.76</v>
+        <v>3.32</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.13</v>
+        <v>3.48</v>
       </c>
       <c r="R23" t="n">
-        <v>2.57</v>
+        <v>2.09</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -4983,10 +4983,10 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AG23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3.32</v>
+        <v>1.66</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.48</v>
+        <v>3.94</v>
       </c>
       <c r="R24" t="n">
-        <v>2.09</v>
+        <v>4.74</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5180,10 +5180,10 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AF24" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="R25" t="n">
-        <v>2.32</v>
+        <v>2.66</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.23</v>
+        <v>4.33</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="R26" t="n">
-        <v>3.26</v>
+        <v>1.73</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5574,10 +5574,10 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.15</v>
+        <v>1.72</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.61</v>
+        <v>1.98</v>
       </c>
       <c r="AG26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.2</v>
+        <v>3.98</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.25</v>
+        <v>3.62</v>
       </c>
       <c r="R27" t="n">
-        <v>3.25</v>
+        <v>1.85</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5771,10 +5771,10 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>4.84</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Jamshedpur</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Jamshedpur</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.94</v>
+        <v>2.73</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.72</v>
+        <v>3.16</v>
       </c>
       <c r="R34" t="n">
-        <v>3.46</v>
+        <v>2.34</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>6.52</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>5.84</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.41</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>5.84</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>6.52</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>2.31</v>
+        <v>1.76</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.9</v>
+        <v>3.91</v>
       </c>
       <c r="R59" t="n">
-        <v>3.08</v>
+        <v>4.58</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12075,10 +12075,10 @@
         <v>0</v>
       </c>
       <c r="AE59" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF59" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1.76</v>
+        <v>2.31</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.91</v>
+        <v>3.9</v>
       </c>
       <c r="R60" t="n">
-        <v>4.58</v>
+        <v>3.08</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF60" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -13361,22 +13361,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>3.76</v>
+        <v>2.58</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="R67" t="n">
-        <v>1.98</v>
+        <v>2.73</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>2.58</v>
+        <v>3.76</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="R68" t="n">
-        <v>2.73</v>
+        <v>1.98</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -13996,17 +13996,17 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,10 +14045,10 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF69" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14390,17 +14390,17 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P71" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14439,10 +14439,10 @@
         <v>0</v>
       </c>
       <c r="AE71" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF71" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG71" t="n">
         <v>0</v>
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF72" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14833,10 +14833,10 @@
         <v>0</v>
       </c>
       <c r="AE73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF73" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG73" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>2.1</v>
+        <v>3.62</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="R75" t="n">
-        <v>3.41</v>
+        <v>1.86</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>3.62</v>
+        <v>2.1</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="R76" t="n">
-        <v>1.86</v>
+        <v>3.41</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2.1</v>
+        <v>2.87</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="R77" t="n">
-        <v>3.35</v>
+        <v>2.3</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>2.37</v>
+        <v>1.68</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.2</v>
+        <v>3.62</v>
       </c>
       <c r="R78" t="n">
-        <v>2.7</v>
+        <v>4.4</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15818,10 +15818,10 @@
         <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF78" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG78" t="n">
         <v>0</v>
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>2.32</v>
+        <v>1.74</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.1</v>
+        <v>3.52</v>
       </c>
       <c r="R79" t="n">
-        <v>2.99</v>
+        <v>4.17</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16015,10 +16015,10 @@
         <v>0</v>
       </c>
       <c r="AE79" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF79" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>4.51</v>
+        <v>1.45</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.58</v>
+        <v>4.05</v>
       </c>
       <c r="R80" t="n">
-        <v>1.77</v>
+        <v>6.12</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16212,10 +16212,10 @@
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF80" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.54</v>
+        <v>3.62</v>
       </c>
       <c r="R81" t="n">
-        <v>3.52</v>
+        <v>4.02</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16409,10 +16409,10 @@
         <v>0</v>
       </c>
       <c r="AE81" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF81" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG81" t="n">
         <v>0</v>
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>1.92</v>
+        <v>2.31</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.91</v>
+        <v>3.16</v>
       </c>
       <c r="R83" t="n">
-        <v>3.71</v>
+        <v>2.86</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="Q84" t="n">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="R84" t="n">
-        <v>2.86</v>
+        <v>2.99</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>1.68</v>
+        <v>2.16</v>
       </c>
       <c r="Q85" t="n">
-        <v>3.62</v>
+        <v>3.5</v>
       </c>
       <c r="R85" t="n">
-        <v>4.4</v>
+        <v>3.14</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17197,10 +17197,10 @@
         <v>0</v>
       </c>
       <c r="AE85" t="n">
-        <v>1.82</v>
+        <v>2.03</v>
       </c>
       <c r="AF85" t="n">
-        <v>1.94</v>
+        <v>1.78</v>
       </c>
       <c r="AG85" t="n">
         <v>0</v>
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>2.16</v>
+        <v>2.37</v>
       </c>
       <c r="Q86" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="R86" t="n">
-        <v>3.14</v>
+        <v>2.7</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17394,10 +17394,10 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF86" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG86" t="n">
         <v>0</v>
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>1.45</v>
+        <v>2.1</v>
       </c>
       <c r="Q87" t="n">
-        <v>4.05</v>
+        <v>3.15</v>
       </c>
       <c r="R87" t="n">
-        <v>6.12</v>
+        <v>3.35</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17591,10 +17591,10 @@
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF87" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG87" t="n">
         <v>0</v>
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>1.74</v>
+        <v>3.74</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.62</v>
+        <v>3.45</v>
       </c>
       <c r="R88" t="n">
-        <v>4.02</v>
+        <v>1.88</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17788,10 +17788,10 @@
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF88" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG88" t="n">
         <v>0</v>
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>3.74</v>
+        <v>2</v>
       </c>
       <c r="Q90" t="n">
-        <v>3.45</v>
+        <v>3.54</v>
       </c>
       <c r="R90" t="n">
-        <v>1.88</v>
+        <v>3.52</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>2.87</v>
+        <v>1.92</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.4</v>
+        <v>3.91</v>
       </c>
       <c r="R91" t="n">
-        <v>2.3</v>
+        <v>3.71</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>1.74</v>
+        <v>4.51</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.52</v>
+        <v>3.58</v>
       </c>
       <c r="R92" t="n">
-        <v>4.17</v>
+        <v>1.77</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18576,10 +18576,10 @@
         <v>0</v>
       </c>
       <c r="AE92" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF92" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG92" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.45</v>
+        <v>4.58</v>
       </c>
       <c r="R93" t="n">
-        <v>3.63</v>
+        <v>7.8</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18773,10 +18773,10 @@
         <v>0</v>
       </c>
       <c r="AE93" t="n">
-        <v>2.15</v>
+        <v>1.68</v>
       </c>
       <c r="AF93" t="n">
-        <v>1.62</v>
+        <v>2.05</v>
       </c>
       <c r="AG93" t="n">
         <v>0</v>
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Q95" t="n">
-        <v>6.15</v>
+        <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>8.949999999999999</v>
+        <v>0</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1.5</v>
+        <v>1.92</v>
       </c>
       <c r="Q96" t="n">
-        <v>4.58</v>
+        <v>3.3</v>
       </c>
       <c r="R96" t="n">
-        <v>7.8</v>
+        <v>4.14</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,10 +19364,10 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF96" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Q97" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="R97" t="n">
-        <v>0</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="Q98" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="R98" t="n">
-        <v>4.14</v>
+        <v>3.63</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19758,10 +19758,10 @@
         <v>0</v>
       </c>
       <c r="AE98" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF98" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG98" t="n">
         <v>0</v>
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q109" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R109" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25181,22 +25181,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25229,13 +25229,13 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q126" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R126" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S126" t="n">
         <v>0</v>
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25575,22 +25575,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25623,13 +25623,13 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q128" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R128" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -25772,22 +25772,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25820,13 +25820,13 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="Q129" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R129" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="S129" t="n">
         <v>0</v>

--- a/jogos_2026-05-01.xlsx
+++ b/jogos_2026-05-01.xlsx
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2028,10 +2028,10 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="R13" t="n">
-        <v>2.43</v>
+        <v>3</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kuching FA</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Kuching FA</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.76</v>
+        <v>4.33</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.13</v>
+        <v>3.8</v>
       </c>
       <c r="R16" t="n">
-        <v>2.57</v>
+        <v>1.73</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3604,10 +3604,10 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="R17" t="n">
-        <v>2.32</v>
+        <v>2.66</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3801,10 +3801,10 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.23</v>
+        <v>1.59</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.2</v>
+        <v>3.98</v>
       </c>
       <c r="R18" t="n">
-        <v>3.26</v>
+        <v>5.35</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -3998,10 +3998,10 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.15</v>
+        <v>1.78</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.61</v>
+        <v>1.9</v>
       </c>
       <c r="AG18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4195,10 +4195,10 @@
         <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.59</v>
+        <v>2.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.98</v>
+        <v>3.25</v>
       </c>
       <c r="R20" t="n">
-        <v>5.35</v>
+        <v>3.25</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4392,10 +4392,10 @@
         <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.78</v>
+        <v>2.1</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AG20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.29</v>
+        <v>2.23</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="R21" t="n">
-        <v>3.21</v>
+        <v>3.26</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.2</v>
+        <v>2.76</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.25</v>
+        <v>3.13</v>
       </c>
       <c r="R22" t="n">
-        <v>3.25</v>
+        <v>2.57</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.1</v>
+        <v>1.66</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>4.74</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5180,10 +5180,10 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.64</v>
+        <v>3.98</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.15</v>
+        <v>3.62</v>
       </c>
       <c r="R25" t="n">
-        <v>2.66</v>
+        <v>1.85</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>4.33</v>
+        <v>2.65</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="R26" t="n">
-        <v>1.73</v>
+        <v>2.32</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5574,10 +5574,10 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>3.98</v>
+        <v>1.66</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.62</v>
+        <v>3.94</v>
       </c>
       <c r="R27" t="n">
-        <v>1.85</v>
+        <v>4.74</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5771,10 +5771,10 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>5.84</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.11</v>
+        <v>4.84</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.42</v>
+        <v>3.65</v>
       </c>
       <c r="R36" t="n">
-        <v>3.25</v>
+        <v>1.64</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>4.84</v>
+        <v>1.38</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.65</v>
+        <v>4.8</v>
       </c>
       <c r="R38" t="n">
-        <v>1.64</v>
+        <v>6.52</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>5.84</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.41</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>6.52</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>3.8</v>
+        <v>2.57</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.45</v>
+        <v>3.19</v>
       </c>
       <c r="R49" t="n">
-        <v>1.85</v>
+        <v>2.68</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.09</v>
+        <v>1.68</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.15</v>
+        <v>4.11</v>
       </c>
       <c r="R58" t="n">
-        <v>3.31</v>
+        <v>4.45</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="R60" t="n">
-        <v>3.08</v>
+        <v>2.75</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.38</v>
+        <v>2.31</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="R61" t="n">
-        <v>2.75</v>
+        <v>3.08</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>2.58</v>
+        <v>2.34</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
       <c r="R67" t="n">
-        <v>2.73</v>
+        <v>2.93</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13651,10 +13651,10 @@
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF67" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG67" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>2.34</v>
+        <v>3.02</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="R69" t="n">
-        <v>2.93</v>
+        <v>2.15</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,10 +14045,10 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF69" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>3.02</v>
+        <v>2.58</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.6</v>
+        <v>3.12</v>
       </c>
       <c r="R70" t="n">
-        <v>2.15</v>
+        <v>2.73</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF72" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14833,10 +14833,10 @@
         <v>0</v>
       </c>
       <c r="AE73" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF73" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG73" t="n">
         <v>0</v>
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2.87</v>
+        <v>1.45</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.4</v>
+        <v>4.05</v>
       </c>
       <c r="R77" t="n">
-        <v>2.3</v>
+        <v>6.12</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15621,10 +15621,10 @@
         <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF77" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG77" t="n">
         <v>0</v>
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>1.68</v>
+        <v>1.92</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.62</v>
+        <v>3.91</v>
       </c>
       <c r="R78" t="n">
-        <v>4.4</v>
+        <v>3.71</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15818,10 +15818,10 @@
         <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF78" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG78" t="n">
         <v>0</v>
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1.74</v>
+        <v>2.31</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.52</v>
+        <v>3.16</v>
       </c>
       <c r="R79" t="n">
-        <v>4.17</v>
+        <v>2.86</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16015,10 +16015,10 @@
         <v>0</v>
       </c>
       <c r="AE79" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF79" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG79" t="n">
         <v>0</v>
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1.45</v>
+        <v>1.74</v>
       </c>
       <c r="Q80" t="n">
-        <v>4.05</v>
+        <v>3.62</v>
       </c>
       <c r="R80" t="n">
-        <v>6.12</v>
+        <v>4.02</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16212,10 +16212,10 @@
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AF80" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AG80" t="n">
         <v>0</v>
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1.74</v>
+        <v>2.1</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.62</v>
+        <v>3.15</v>
       </c>
       <c r="R81" t="n">
-        <v>4.02</v>
+        <v>3.35</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16409,10 +16409,10 @@
         <v>0</v>
       </c>
       <c r="AE81" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF81" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG81" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Q82" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R82" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="R83" t="n">
-        <v>2.86</v>
+        <v>2.99</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>2.32</v>
+        <v>4.51</v>
       </c>
       <c r="Q84" t="n">
-        <v>3.1</v>
+        <v>3.58</v>
       </c>
       <c r="R84" t="n">
-        <v>2.99</v>
+        <v>1.77</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>2.1</v>
+        <v>1.42</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.15</v>
+        <v>4.3</v>
       </c>
       <c r="R87" t="n">
-        <v>3.35</v>
+        <v>6.55</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>3.74</v>
+        <v>1.68</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.45</v>
+        <v>3.62</v>
       </c>
       <c r="R88" t="n">
-        <v>1.88</v>
+        <v>4.4</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17788,10 +17788,10 @@
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF88" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG88" t="n">
         <v>0</v>
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>1.42</v>
+        <v>2</v>
       </c>
       <c r="Q89" t="n">
-        <v>4.3</v>
+        <v>3.54</v>
       </c>
       <c r="R89" t="n">
-        <v>6.55</v>
+        <v>3.52</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="Q90" t="n">
-        <v>3.54</v>
+        <v>3.52</v>
       </c>
       <c r="R90" t="n">
-        <v>3.52</v>
+        <v>4.17</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18182,10 +18182,10 @@
         <v>0</v>
       </c>
       <c r="AE90" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF90" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG90" t="n">
         <v>0</v>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-  